--- a/deliverables/deliverables-20260120-0030/Model_1_CCGT.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_1_CCGT.xlsx
@@ -2815,6 +2815,63 @@
         <v/>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>Scheduled DS (for DSRA)</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>Based on straight-line amort, no sweep</t>
+        </is>
+      </c>
+      <c r="E93" s="18">
+        <f>MAX(0,$D$55-(1-1)*$D$57)*$D$40+$D$57</f>
+        <v/>
+      </c>
+      <c r="F93" s="18">
+        <f>MAX(0,$D$55-(2-1)*$D$57)*$D$40+$D$57</f>
+        <v/>
+      </c>
+      <c r="G93" s="18">
+        <f>MAX(0,$D$55-(3-1)*$D$57)*$D$40+$D$57</f>
+        <v/>
+      </c>
+      <c r="H93" s="18">
+        <f>MAX(0,$D$55-(4-1)*$D$57)*$D$40+$D$57</f>
+        <v/>
+      </c>
+      <c r="I93" s="18">
+        <f>MAX(0,$D$55-(5-1)*$D$57)*$D$40+$D$57</f>
+        <v/>
+      </c>
+      <c r="J93" s="18">
+        <f>MAX(0,$D$55-(6-1)*$D$57)*$D$40+$D$57</f>
+        <v/>
+      </c>
+      <c r="K93" s="18">
+        <f>MAX(0,$D$55-(7-1)*$D$57)*$D$40+$D$57</f>
+        <v/>
+      </c>
+      <c r="L93" s="18">
+        <f>MAX(0,$D$55-(8-1)*$D$57)*$D$40+$D$57</f>
+        <v/>
+      </c>
+      <c r="M93" s="18">
+        <f>MAX(0,$D$55-(9-1)*$D$57)*$D$40+$D$57</f>
+        <v/>
+      </c>
+      <c r="N93" s="18">
+        <f>MAX(0,$D$55-(10-1)*$D$57)*$D$40+$D$57</f>
+        <v/>
+      </c>
+    </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
@@ -2848,47 +2905,47 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>Next Yr DS × DSRA Months / 12</t>
+          <t>Next Yr Scheduled DS × DSRA Months / 12</t>
         </is>
       </c>
       <c r="D96" s="18">
-        <f>E87*$D$42/12</f>
+        <f>E93*$D$42/12</f>
         <v/>
       </c>
       <c r="E96" s="18">
-        <f>F87*$D$42/12</f>
+        <f>F93*$D$42/12</f>
         <v/>
       </c>
       <c r="F96" s="18">
-        <f>G87*$D$42/12</f>
+        <f>G93*$D$42/12</f>
         <v/>
       </c>
       <c r="G96" s="18">
-        <f>H87*$D$42/12</f>
+        <f>H93*$D$42/12</f>
         <v/>
       </c>
       <c r="H96" s="18">
-        <f>I87*$D$42/12</f>
+        <f>I93*$D$42/12</f>
         <v/>
       </c>
       <c r="I96" s="18">
-        <f>J87*$D$42/12</f>
+        <f>J93*$D$42/12</f>
         <v/>
       </c>
       <c r="J96" s="18">
-        <f>K87*$D$42/12</f>
+        <f>K93*$D$42/12</f>
         <v/>
       </c>
       <c r="K96" s="18">
-        <f>L87*$D$42/12</f>
+        <f>L93*$D$42/12</f>
         <v/>
       </c>
       <c r="L96" s="18">
-        <f>M87*$D$42/12</f>
+        <f>M93*$D$42/12</f>
         <v/>
       </c>
       <c r="M96" s="18">
-        <f>N87*$D$42/12</f>
+        <f>N93*$D$42/12</f>
         <v/>
       </c>
       <c r="N96" s="18">

--- a/deliverables/deliverables-20260120-0030/Model_1_CCGT.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_1_CCGT.xlsx
@@ -1835,43 +1835,43 @@
         </is>
       </c>
       <c r="E69" s="18">
-        <f>$D$54*$D$24*E63/1000000000</f>
+        <f>$D$54*$D$24*E63/1E9</f>
         <v/>
       </c>
       <c r="F69" s="18">
-        <f>$D$54*$D$24*F63/1000000000</f>
+        <f>$D$54*$D$24*F63/1E9</f>
         <v/>
       </c>
       <c r="G69" s="18">
-        <f>$D$54*$D$24*G63/1000000000</f>
+        <f>$D$54*$D$24*G63/1E9</f>
         <v/>
       </c>
       <c r="H69" s="18">
-        <f>$D$54*$D$24*H63/1000000000</f>
+        <f>$D$54*$D$24*H63/1E9</f>
         <v/>
       </c>
       <c r="I69" s="18">
-        <f>$D$54*$D$24*I63/1000000000</f>
+        <f>$D$54*$D$24*I63/1E9</f>
         <v/>
       </c>
       <c r="J69" s="18">
-        <f>$D$54*$D$24*J63/1000000000</f>
+        <f>$D$54*$D$24*J63/1E9</f>
         <v/>
       </c>
       <c r="K69" s="18">
-        <f>$D$54*$D$24*K63/1000000000</f>
+        <f>$D$54*$D$24*K63/1E9</f>
         <v/>
       </c>
       <c r="L69" s="18">
-        <f>$D$54*$D$24*L63/1000000000</f>
+        <f>$D$54*$D$24*L63/1E9</f>
         <v/>
       </c>
       <c r="M69" s="18">
-        <f>$D$54*$D$24*M63/1000000000</f>
+        <f>$D$54*$D$24*M63/1E9</f>
         <v/>
       </c>
       <c r="N69" s="18">
-        <f>$D$54*$D$24*N63/1000000000</f>
+        <f>$D$54*$D$24*N63/1E9</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Model_1_CCGT.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_1_CCGT.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,11 +19,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0.0_);(#,##0.0)"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +53,21 @@
     <font>
       <b val="1"/>
       <color rgb="000000FF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -104,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -117,12 +133,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -133,6 +149,14 @@
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -207,6 +231,261 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Lotus Infrastructure</author>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0" shapeId="0">
+      <text>
+        <t>Enterprise Value = Equity + Debt. Represents total asset value regardless of financing structure. Key input for returns analysis.</t>
+      </text>
+    </comment>
+    <comment ref="C4" authorId="0" shapeId="0">
+      <text>
+        <t>Earnings Before Interest, Taxes, Depreciation, Amortization. Cash earnings available to service debt and pay equity.</t>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0" shapeId="0">
+      <text>
+        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal. DSCR = CFADS ÷ DS.</t>
+      </text>
+    </comment>
+    <comment ref="C6" authorId="0" shapeId="0">
+      <text>
+        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+      </text>
+    </comment>
+    <comment ref="C7" authorId="0" shapeId="0">
+      <text>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+      </text>
+    </comment>
+    <comment ref="C8" authorId="0" shapeId="0">
+      <text>
+        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money. Less sensitive to timing than IRR.</t>
+      </text>
+    </comment>
+    <comment ref="C9" authorId="0" shapeId="0">
+      <text>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+      </text>
+    </comment>
+    <comment ref="C13" authorId="0" shapeId="0">
+      <text>
+        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+      </text>
+    </comment>
+    <comment ref="C17" authorId="0" shapeId="0">
+      <text>
+        <t>Enterprise Value = Equity + Debt. Represents total asset value regardless of financing structure. Key input for returns analysis.</t>
+      </text>
+    </comment>
+    <comment ref="C18" authorId="0" shapeId="0">
+      <text>
+        <t>Typical 1-2% of EV for legal, accounting, advisory fees. Funded at close, increases total uses.</t>
+      </text>
+    </comment>
+    <comment ref="C19" authorId="0" shapeId="0">
+      <text>
+        <t>Assumed sale multiple at exit. Conservative approach: use entry multiple. Upside case: multiple expansion from derisking.</t>
+      </text>
+    </comment>
+    <comment ref="C20" authorId="0" shapeId="0">
+      <text>
+        <t>Typical PE hold is 5-7 years. Often aligned with debt tenor to avoid refinancing risk.</t>
+      </text>
+    </comment>
+    <comment ref="C23" authorId="0" shapeId="0">
+      <text>
+        <t>Maximum output rating. Used to calculate generation and capacity revenue. Actual dispatch varies with economics.</t>
+      </text>
+    </comment>
+    <comment ref="C24" authorId="0" shapeId="0">
+      <text>
+        <t>Measures thermal efficiency. 7,000 Btu/kWh is efficient modern CCGT. Higher HR = less efficient = higher fuel cost per MWh.</t>
+      </text>
+    </comment>
+    <comment ref="C25" authorId="0" shapeId="0">
+      <text>
+        <t>Maximum output rating. Used to calculate generation and capacity revenue. Actual dispatch varies with economics.</t>
+      </text>
+    </comment>
+    <comment ref="C26" authorId="0" shapeId="0">
+      <text>
+        <t>Reduces UCAP (capacity revenue). Lenders/buyers discount nameplate by this factor. 5% is typical well-maintained plant.</t>
+      </text>
+    </comment>
+    <comment ref="C30" authorId="0" shapeId="0">
+      <text>
+        <t>Maximum output rating. Used to calculate generation and capacity revenue. Actual dispatch varies with economics.</t>
+      </text>
+    </comment>
+    <comment ref="C39" authorId="0" shapeId="0">
+      <text>
+        <t>Higher leverage amplifies equity returns but increases risk. Merchant assets: 40-50%. Contracted: 60-70%.</t>
+      </text>
+    </comment>
+    <comment ref="C40" authorId="0" shapeId="0">
+      <text>
+        <t>Includes spread over benchmark (SOFR). Investment grade infra: 150-250 bps spread. Sub-IG: 300-500 bps.</t>
+      </text>
+    </comment>
+    <comment ref="C41" authorId="0" shapeId="0">
+      <text>
+        <t>Shorter tenor = faster amortization = lower refinancing risk but higher annual debt service.</t>
+      </text>
+    </comment>
+    <comment ref="C42" authorId="0" shapeId="0">
+      <text>
+        <t>6 months is market standard. Provides lender runway if borrower misses payment. Funded at close.</t>
+      </text>
+    </comment>
+    <comment ref="C43" authorId="0" shapeId="0">
+      <text>
+        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
+      </text>
+    </comment>
+    <comment ref="C44" authorId="0" shapeId="0">
+      <text>
+        <t>If DSCR falls below this level, cash is trapped and cannot be distributed to equity. Typically 1.10-1.15x.</t>
+      </text>
+    </comment>
+    <comment ref="C47" authorId="0" shapeId="0">
+      <text>
+        <t>US federal ~21% + state. Use blended effective rate. Shields reduce taxable income.</t>
+      </text>
+    </comment>
+    <comment ref="C48" authorId="0" shapeId="0">
+      <text>
+        <t>Excludes land (~15% of EV). Depreciation creates tax shield, improves after-tax cash flow.</t>
+      </text>
+    </comment>
+    <comment ref="C53" authorId="0" shapeId="0">
+      <text>
+        <t>Maximum output rating. Used to calculate generation and capacity revenue. Actual dispatch varies with economics.</t>
+      </text>
+    </comment>
+    <comment ref="C54" authorId="0" shapeId="0">
+      <text>
+        <t>Annual MWh output. CF reflects expected dispatch based on merit order. 8760 = hours/year. 55% CF = ~4800 hrs/yr.</t>
+      </text>
+    </comment>
+    <comment ref="C62" authorId="0" shapeId="0">
+      <text>
+        <t>Maximum output rating. Used to calculate generation and capacity revenue. Actual dispatch varies with economics.</t>
+      </text>
+    </comment>
+    <comment ref="C65" authorId="0" shapeId="0">
+      <text>
+        <t>Merchant energy revenue from selling MWh into wholesale market. Divide by 1E6 to convert $ to $mm.</t>
+      </text>
+    </comment>
+    <comment ref="C66" authorId="0" shapeId="0">
+      <text>
+        <t>Maximum output rating. Used to calculate generation and capacity revenue. Actual dispatch varies with economics.</t>
+      </text>
+    </comment>
+    <comment ref="C69" authorId="0" shapeId="0">
+      <text>
+        <t>Largest variable cost for thermal plants. HR measures efficiency. Divide by 1E9: MWh × Btu/kWh × $/mmBtu → $mm.</t>
+      </text>
+    </comment>
+    <comment ref="C74" authorId="0" shapeId="0">
+      <text>
+        <t>Earnings Before Interest, Taxes, Depreciation, Amortization. Cash earnings available to service debt and pay equity.</t>
+      </text>
+    </comment>
+    <comment ref="C80" authorId="0" shapeId="0">
+      <text>
+        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal. DSCR = CFADS ÷ DS.</t>
+      </text>
+    </comment>
+    <comment ref="C83" authorId="0" shapeId="0">
+      <text>
+        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
+      </text>
+    </comment>
+    <comment ref="C84" authorId="0" shapeId="0">
+      <text>
+        <t>Debt outstanding at start of year. Decreases as principal is paid or swept.</t>
+      </text>
+    </comment>
+    <comment ref="C85" authorId="0" shapeId="0">
+      <text>
+        <t>Interest accrues on outstanding balance. As principal amortizes, interest drops — the deleveraging benefit to equity.</t>
+      </text>
+    </comment>
+    <comment ref="C87" authorId="0" shapeId="0">
+      <text>
+        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
+      </text>
+    </comment>
+    <comment ref="C89" authorId="0" shapeId="0">
+      <text>
+        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
+      </text>
+    </comment>
+    <comment ref="C91" authorId="0" shapeId="0">
+      <text>
+        <t>Debt remaining after payments. Should reach zero by tenor end. MAX(0,...) prevents negative balance.</t>
+      </text>
+    </comment>
+    <comment ref="C92" authorId="0" shapeId="0">
+      <text>
+        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+      </text>
+    </comment>
+    <comment ref="C93" authorId="0" shapeId="0">
+      <text>
+        <t>Debt service using straight-line principal only (no sweep). Used for DSRA target to avoid circular reference.</t>
+      </text>
+    </comment>
+    <comment ref="C96" authorId="0" shapeId="0">
+      <text>
+        <t>Reserve sized to cover NEXT years debt service. Uses SCHEDULED DS (not actual) to avoid circular reference. Released at exit.</t>
+      </text>
+    </comment>
+    <comment ref="C98" authorId="0" shapeId="0">
+      <text>
+        <t>Positive = funding requirement (reduces distributable). Negative = release (increases distributable).</t>
+      </text>
+    </comment>
+    <comment ref="C105" authorId="0" shapeId="0">
+      <text>
+        <t>Cash available to equity after debt service and DSRA. Trapped if DSCR below lock-up threshold.</t>
+      </text>
+    </comment>
+    <comment ref="C111" authorId="0" shapeId="0">
+      <text>
+        <t>Typical 1-2% of EV for legal, accounting, advisory fees. Funded at close, increases total uses.</t>
+      </text>
+    </comment>
+    <comment ref="C112" authorId="0" shapeId="0">
+      <text>
+        <t>Positive = funding requirement (reduces distributable). Negative = release (increases distributable).</t>
+      </text>
+    </comment>
+    <comment ref="C130" authorId="0" shapeId="0">
+      <text>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+      </text>
+    </comment>
+    <comment ref="C131" authorId="0" shapeId="0">
+      <text>
+        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money. Less sensitive to timing than IRR.</t>
+      </text>
+    </comment>
+    <comment ref="C135" authorId="0" shapeId="0">
+      <text>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -588,7 +867,11 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr"/>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Purchase price for asset</t>
+        </is>
+      </c>
       <c r="D3" s="7">
         <f>$D$17</f>
         <v/>
@@ -605,7 +888,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr"/>
+      <c r="C4" s="6">
+        <f> Revenue − OpEx</f>
+        <v/>
+      </c>
       <c r="D4" s="7">
         <f>E74</f>
         <v/>
@@ -622,7 +908,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr"/>
+      <c r="C5" s="6">
+        <f> EBITDA − Taxes</f>
+        <v/>
+      </c>
       <c r="D5" s="7">
         <f>AVERAGE(E80:K80)</f>
         <v/>
@@ -639,8 +928,11 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr"/>
-      <c r="D6" s="8">
+      <c r="C6" s="6">
+        <f> CFADS / Debt Service</f>
+        <v/>
+      </c>
+      <c r="D6" s="24">
         <f>MIN(E92:K92)</f>
         <v/>
       </c>
@@ -656,8 +948,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="9">
+      <c r="C7" s="6">
+        <f> IRR(Equity CF)</f>
+        <v/>
+      </c>
+      <c r="D7" s="25">
         <f>D130</f>
         <v/>
       </c>
@@ -673,8 +968,11 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="8">
+      <c r="C8" s="6">
+        <f> Total In / Total Out</f>
+        <v/>
+      </c>
+      <c r="D8" s="24">
         <f>D131</f>
         <v/>
       </c>
@@ -690,8 +988,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="9">
+      <c r="C9" s="6">
+        <f> IRR(Equity CF)</f>
+        <v/>
+      </c>
+      <c r="D9" s="25">
         <f>D135</f>
         <v/>
       </c>
@@ -749,7 +1050,10 @@
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr"/>
-      <c r="C13" s="6" t="inlineStr"/>
+      <c r="C13" s="6">
+        <f> CFADS / Debt Service</f>
+        <v/>
+      </c>
       <c r="D13" s="10">
         <f>IF(D6&gt;=1.25,"PASS","FAIL")</f>
         <v/>
@@ -811,7 +1115,7 @@
           <t>Legal, advisory, financing</t>
         </is>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" s="26" t="n">
         <v>0.015</v>
       </c>
     </row>
@@ -831,7 +1135,7 @@
           <t>On exit year EBITDA</t>
         </is>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="27" t="n">
         <v>7</v>
       </c>
     </row>
@@ -931,7 +1235,7 @@
           <t>Annual utilization</t>
         </is>
       </c>
-      <c r="D25" s="12" t="n">
+      <c r="D25" s="26" t="n">
         <v>0.55</v>
       </c>
     </row>
@@ -951,7 +1255,7 @@
           <t>Unplanned downtime</t>
         </is>
       </c>
-      <c r="D26" s="12" t="n">
+      <c r="D26" s="26" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -1051,7 +1355,7 @@
           <t>Applied to all prices/costs</t>
         </is>
       </c>
-      <c r="D32" s="12" t="n">
+      <c r="D32" s="26" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -1151,7 +1455,7 @@
           <t>Debt / Entry EV</t>
         </is>
       </c>
-      <c r="D39" s="12" t="n">
+      <c r="D39" s="26" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -1171,7 +1475,7 @@
           <t>All-in borrowing cost</t>
         </is>
       </c>
-      <c r="D40" s="12" t="n">
+      <c r="D40" s="26" t="n">
         <v>0.065</v>
       </c>
     </row>
@@ -1231,7 +1535,7 @@
           <t>Mandatory excess CF prepay</t>
         </is>
       </c>
-      <c r="D43" s="12" t="n">
+      <c r="D43" s="26" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -1251,7 +1555,7 @@
           <t>Distribution threshold</t>
         </is>
       </c>
-      <c r="D44" s="13" t="n">
+      <c r="D44" s="27" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -1291,7 +1595,7 @@
           <t>Blended federal + state</t>
         </is>
       </c>
-      <c r="D47" s="12" t="n">
+      <c r="D47" s="26" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -1311,7 +1615,7 @@
           <t>% of EV for depreciation</t>
         </is>
       </c>
-      <c r="D48" s="12" t="n">
+      <c r="D48" s="26" t="n">
         <v>0.85</v>
       </c>
     </row>
@@ -1550,7 +1854,7 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>Escalated</t>
+          <t>Nameplate MW</t>
         </is>
       </c>
       <c r="E62" s="18">
@@ -2053,7 +2357,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C74" s="6" t="inlineStr"/>
+      <c r="C74" s="6">
+        <f> Revenue − OpEx</f>
+        <v/>
+      </c>
       <c r="E74" s="7">
         <f>E67-E72</f>
         <v/>
@@ -2293,7 +2600,11 @@
         </is>
       </c>
       <c r="B83" s="4" t="n"/>
-      <c r="C83" s="4" t="n"/>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>% of excess cash to prepay</t>
+        </is>
+      </c>
       <c r="D83" s="4" t="n"/>
       <c r="E83" s="4" t="n"/>
       <c r="F83" s="4" t="n"/>
@@ -2317,7 +2628,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C84" s="6" t="inlineStr"/>
+      <c r="C84" s="6">
+        <f> Prior Yr End Bal</f>
+        <v/>
+      </c>
       <c r="E84" s="18">
         <f>$D$55</f>
         <v/>
@@ -2774,43 +3088,43 @@
           <t>CFADS / Debt Service</t>
         </is>
       </c>
-      <c r="E92" s="8">
+      <c r="E92" s="24">
         <f>IF(E87&gt;0,E80/E87,0)</f>
         <v/>
       </c>
-      <c r="F92" s="8">
+      <c r="F92" s="24">
         <f>IF(F87&gt;0,F80/F87,0)</f>
         <v/>
       </c>
-      <c r="G92" s="8">
+      <c r="G92" s="24">
         <f>IF(G87&gt;0,G80/G87,0)</f>
         <v/>
       </c>
-      <c r="H92" s="8">
+      <c r="H92" s="24">
         <f>IF(H87&gt;0,H80/H87,0)</f>
         <v/>
       </c>
-      <c r="I92" s="8">
+      <c r="I92" s="24">
         <f>IF(I87&gt;0,I80/I87,0)</f>
         <v/>
       </c>
-      <c r="J92" s="8">
+      <c r="J92" s="24">
         <f>IF(J87&gt;0,J80/J87,0)</f>
         <v/>
       </c>
-      <c r="K92" s="8">
+      <c r="K92" s="24">
         <f>IF(K87&gt;0,K80/K87,0)</f>
         <v/>
       </c>
-      <c r="L92" s="8">
+      <c r="L92" s="24">
         <f>IF(L87&gt;0,L80/L87,0)</f>
         <v/>
       </c>
-      <c r="M92" s="8">
+      <c r="M92" s="24">
         <f>IF(M87&gt;0,M80/M87,0)</f>
         <v/>
       </c>
-      <c r="N92" s="8">
+      <c r="N92" s="24">
         <f>IF(N87&gt;0,N80/N87,0)</f>
         <v/>
       </c>
@@ -3376,7 +3690,11 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C111" s="6" t="inlineStr"/>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>% of EV for legal, advisory</t>
+        </is>
+      </c>
       <c r="D111" s="18">
         <f>$D$17*$D$18</f>
         <v/>
@@ -3393,7 +3711,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C112" s="6" t="inlineStr"/>
+      <c r="C112" s="6">
+        <f> Target − Beginning</f>
+        <v/>
+      </c>
       <c r="D112" s="18">
         <f>D96</f>
         <v/>
@@ -3685,8 +4006,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C130" s="6" t="inlineStr"/>
-      <c r="D130" s="9">
+      <c r="C130" s="6">
+        <f> IRR(Equity CF)</f>
+        <v/>
+      </c>
+      <c r="D130" s="25">
         <f>IRR(D129:K129)</f>
         <v/>
       </c>
@@ -3707,7 +4031,7 @@
           <t>Sum inflows / outflow</t>
         </is>
       </c>
-      <c r="D131" s="8">
+      <c r="D131" s="24">
         <f>SUMIF(D129:K129,"&gt;0")/ABS(D129)</f>
         <v/>
       </c>
@@ -3789,10 +4113,204 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C135" s="6" t="inlineStr"/>
-      <c r="D135" s="9">
+      <c r="C135" s="6">
+        <f> IRR(Equity CF)</f>
+        <v/>
+      </c>
+      <c r="D135" s="25">
         <f>IRR(D134:K134)</f>
         <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="90" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>INVESTMENT COMMITTEE MEMORANDUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Greenfield CCGT Power Station</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>EXECUTIVE SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>• Acquire 365 MW combined-cycle gas turbine at $520mm ($1,425/kW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>• Mid-merit dispatch profile with 55% capacity factor</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>• Dual revenue streams: energy ($45/MWh) + capacity ($75/kW-yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>• Target returns: 12-14% levered IRR, 1.8-2.0x MOIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1"/>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>1. Efficient heat rate provides dispatch advantage</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   At 7,000 Btu/kWh, plant dispatches ahead of older, less efficient fleet. Structural cost advantage in merit order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>2. Capacity revenue provides downside protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   40% of revenue from capacity payments regardless of dispatch. Reduces merchant exposure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>3. Cash sweep structure accelerates deleveraging</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   75% mandatory sweep rapidly pays down debt, reducing refinancing risk and building equity cushion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1"/>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>KEY RISKS &amp; MITIGANTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>Risk | Mitigant</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>Gas price volatility | Hedge via heat rate call options; PPA negotiations</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t>Regulatory changes | Monitor capacity market reforms; diversify across ISOs</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>Execution risk | Experienced operator; performance guarantees</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1"/>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="29" t="inlineStr">
+        <is>
+          <t>FINANCIAL SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="30" t="inlineStr">
+        <is>
+          <t>Entry EV: $520mm | Leverage: 45% | Min DSCR: 1.29x</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>Levered IRR: 12.0% | MOIC: 1.75x</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1"/>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="29" t="inlineStr">
+        <is>
+          <t>RECOMMENDATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="30" t="inlineStr">
+        <is>
+          <t>Recommend APPROVAL subject to satisfactory completion of confirmatory due diligence.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/deliverables/deliverables-20260120-0030/Model_1_CCGT.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_1_CCGT.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +22,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,21 +52,6 @@
     <font>
       <b val="1"/>
       <color rgb="000000FF"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -120,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -153,10 +137,6 @@
     <xf numFmtId="166" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -241,247 +221,112 @@
   <commentList>
     <comment ref="C3" authorId="0" shapeId="0">
       <text>
-        <t>Enterprise Value = Equity + Debt. Represents total asset value regardless of financing structure. Key input for returns analysis.</t>
+        <t>Enterprise Value = Equity + Debt. Represents total asset value regardless of financing structure.</t>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>Earnings Before Interest, Taxes, Depreciation, Amortization. Cash earnings available to service debt and pay equity.</t>
+        <t>Cash earnings before financing. What is available to service debt and pay equity.</t>
       </text>
     </comment>
     <comment ref="C5" authorId="0" shapeId="0">
       <text>
-        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal. DSCR = CFADS ÷ DS.</t>
+        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal.</t>
       </text>
     </comment>
     <comment ref="C6" authorId="0" shapeId="0">
       <text>
-        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+        <t>Debt Service Coverage Ratio. Key lender metric. Target: 1.25-1.40x.</t>
       </text>
     </comment>
     <comment ref="C7" authorId="0" shapeId="0">
       <text>
-        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra).</t>
       </text>
     </comment>
     <comment ref="C8" authorId="0" shapeId="0">
       <text>
-        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money. Less sensitive to timing than IRR.</t>
+        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money.</t>
       </text>
     </comment>
     <comment ref="C9" authorId="0" shapeId="0">
       <text>
-        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra).</t>
       </text>
     </comment>
     <comment ref="C13" authorId="0" shapeId="0">
       <text>
-        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+        <t>Debt Service Coverage Ratio. Key lender metric. Target: 1.25-1.40x.</t>
       </text>
     </comment>
     <comment ref="C17" authorId="0" shapeId="0">
       <text>
-        <t>Enterprise Value = Equity + Debt. Represents total asset value regardless of financing structure. Key input for returns analysis.</t>
-      </text>
-    </comment>
-    <comment ref="C18" authorId="0" shapeId="0">
-      <text>
-        <t>Typical 1-2% of EV for legal, accounting, advisory fees. Funded at close, increases total uses.</t>
-      </text>
-    </comment>
-    <comment ref="C19" authorId="0" shapeId="0">
-      <text>
-        <t>Assumed sale multiple at exit. Conservative approach: use entry multiple. Upside case: multiple expansion from derisking.</t>
-      </text>
-    </comment>
-    <comment ref="C20" authorId="0" shapeId="0">
-      <text>
-        <t>Typical PE hold is 5-7 years. Often aligned with debt tenor to avoid refinancing risk.</t>
-      </text>
-    </comment>
-    <comment ref="C23" authorId="0" shapeId="0">
-      <text>
-        <t>Maximum output rating. Used to calculate generation and capacity revenue. Actual dispatch varies with economics.</t>
-      </text>
-    </comment>
-    <comment ref="C24" authorId="0" shapeId="0">
-      <text>
-        <t>Measures thermal efficiency. 7,000 Btu/kWh is efficient modern CCGT. Higher HR = less efficient = higher fuel cost per MWh.</t>
-      </text>
-    </comment>
-    <comment ref="C25" authorId="0" shapeId="0">
-      <text>
-        <t>Maximum output rating. Used to calculate generation and capacity revenue. Actual dispatch varies with economics.</t>
-      </text>
-    </comment>
-    <comment ref="C26" authorId="0" shapeId="0">
-      <text>
-        <t>Reduces UCAP (capacity revenue). Lenders/buyers discount nameplate by this factor. 5% is typical well-maintained plant.</t>
-      </text>
-    </comment>
-    <comment ref="C30" authorId="0" shapeId="0">
-      <text>
-        <t>Maximum output rating. Used to calculate generation and capacity revenue. Actual dispatch varies with economics.</t>
-      </text>
-    </comment>
-    <comment ref="C39" authorId="0" shapeId="0">
-      <text>
-        <t>Higher leverage amplifies equity returns but increases risk. Merchant assets: 40-50%. Contracted: 60-70%.</t>
-      </text>
-    </comment>
-    <comment ref="C40" authorId="0" shapeId="0">
-      <text>
-        <t>Includes spread over benchmark (SOFR). Investment grade infra: 150-250 bps spread. Sub-IG: 300-500 bps.</t>
-      </text>
-    </comment>
-    <comment ref="C41" authorId="0" shapeId="0">
-      <text>
-        <t>Shorter tenor = faster amortization = lower refinancing risk but higher annual debt service.</t>
-      </text>
-    </comment>
-    <comment ref="C42" authorId="0" shapeId="0">
-      <text>
-        <t>6 months is market standard. Provides lender runway if borrower misses payment. Funded at close.</t>
+        <t>Enterprise Value = Equity + Debt. Represents total asset value regardless of financing structure.</t>
       </text>
     </comment>
     <comment ref="C43" authorId="0" shapeId="0">
       <text>
-        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
+        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets.</t>
       </text>
     </comment>
     <comment ref="C44" authorId="0" shapeId="0">
       <text>
-        <t>If DSCR falls below this level, cash is trapped and cannot be distributed to equity. Typically 1.10-1.15x.</t>
-      </text>
-    </comment>
-    <comment ref="C47" authorId="0" shapeId="0">
-      <text>
-        <t>US federal ~21% + state. Use blended effective rate. Shields reduce taxable income.</t>
-      </text>
-    </comment>
-    <comment ref="C48" authorId="0" shapeId="0">
-      <text>
-        <t>Excludes land (~15% of EV). Depreciation creates tax shield, improves after-tax cash flow.</t>
-      </text>
-    </comment>
-    <comment ref="C53" authorId="0" shapeId="0">
-      <text>
-        <t>Maximum output rating. Used to calculate generation and capacity revenue. Actual dispatch varies with economics.</t>
-      </text>
-    </comment>
-    <comment ref="C54" authorId="0" shapeId="0">
-      <text>
-        <t>Annual MWh output. CF reflects expected dispatch based on merit order. 8760 = hours/year. 55% CF = ~4800 hrs/yr.</t>
-      </text>
-    </comment>
-    <comment ref="C62" authorId="0" shapeId="0">
-      <text>
-        <t>Maximum output rating. Used to calculate generation and capacity revenue. Actual dispatch varies with economics.</t>
-      </text>
-    </comment>
-    <comment ref="C65" authorId="0" shapeId="0">
-      <text>
-        <t>Merchant energy revenue from selling MWh into wholesale market. Divide by 1E6 to convert $ to $mm.</t>
-      </text>
-    </comment>
-    <comment ref="C66" authorId="0" shapeId="0">
-      <text>
-        <t>Maximum output rating. Used to calculate generation and capacity revenue. Actual dispatch varies with economics.</t>
+        <t>Debt Service Coverage Ratio. Key lender metric. Target: 1.25-1.40x.</t>
       </text>
     </comment>
     <comment ref="C69" authorId="0" shapeId="0">
       <text>
-        <t>Largest variable cost for thermal plants. HR measures efficiency. Divide by 1E9: MWh × Btu/kWh × $/mmBtu → $mm.</t>
+        <t>Largest variable cost for thermal plants. Divide by 1E9 to convert to $mm.</t>
       </text>
     </comment>
     <comment ref="C74" authorId="0" shapeId="0">
       <text>
-        <t>Earnings Before Interest, Taxes, Depreciation, Amortization. Cash earnings available to service debt and pay equity.</t>
+        <t>Cash earnings before financing. What is available to service debt and pay equity.</t>
       </text>
     </comment>
     <comment ref="C80" authorId="0" shapeId="0">
       <text>
-        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal. DSCR = CFADS ÷ DS.</t>
+        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal.</t>
       </text>
     </comment>
     <comment ref="C83" authorId="0" shapeId="0">
       <text>
-        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
-      </text>
-    </comment>
-    <comment ref="C84" authorId="0" shapeId="0">
-      <text>
-        <t>Debt outstanding at start of year. Decreases as principal is paid or swept.</t>
-      </text>
-    </comment>
-    <comment ref="C85" authorId="0" shapeId="0">
-      <text>
-        <t>Interest accrues on outstanding balance. As principal amortizes, interest drops — the deleveraging benefit to equity.</t>
-      </text>
-    </comment>
-    <comment ref="C87" authorId="0" shapeId="0">
-      <text>
-        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
+        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets.</t>
       </text>
     </comment>
     <comment ref="C89" authorId="0" shapeId="0">
       <text>
-        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
-      </text>
-    </comment>
-    <comment ref="C91" authorId="0" shapeId="0">
-      <text>
-        <t>Debt remaining after payments. Should reach zero by tenor end. MAX(0,...) prevents negative balance.</t>
+        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets.</t>
       </text>
     </comment>
     <comment ref="C92" authorId="0" shapeId="0">
       <text>
-        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+        <t>Debt Service Coverage Ratio. Key lender metric. Target: 1.25-1.40x.</t>
       </text>
     </comment>
     <comment ref="C93" authorId="0" shapeId="0">
       <text>
-        <t>Debt service using straight-line principal only (no sweep). Used for DSRA target to avoid circular reference.</t>
+        <t>Debt service using straight-line principal only. Used for DSRA to avoid circularity.</t>
       </text>
     </comment>
     <comment ref="C96" authorId="0" shapeId="0">
       <text>
-        <t>Reserve sized to cover NEXT years debt service. Uses SCHEDULED DS (not actual) to avoid circular reference. Released at exit.</t>
-      </text>
-    </comment>
-    <comment ref="C98" authorId="0" shapeId="0">
-      <text>
-        <t>Positive = funding requirement (reduces distributable). Negative = release (increases distributable).</t>
-      </text>
-    </comment>
-    <comment ref="C105" authorId="0" shapeId="0">
-      <text>
-        <t>Cash available to equity after debt service and DSRA. Trapped if DSCR below lock-up threshold.</t>
-      </text>
-    </comment>
-    <comment ref="C111" authorId="0" shapeId="0">
-      <text>
-        <t>Typical 1-2% of EV for legal, accounting, advisory fees. Funded at close, increases total uses.</t>
-      </text>
-    </comment>
-    <comment ref="C112" authorId="0" shapeId="0">
-      <text>
-        <t>Positive = funding requirement (reduces distributable). Negative = release (increases distributable).</t>
+        <t>Reserve sized to cover NEXT years debt service. Uses SCHEDULED DS to avoid circular reference.</t>
       </text>
     </comment>
     <comment ref="C130" authorId="0" shapeId="0">
       <text>
-        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra).</t>
       </text>
     </comment>
     <comment ref="C131" authorId="0" shapeId="0">
       <text>
-        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money. Less sensitive to timing than IRR.</t>
+        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money.</t>
       </text>
     </comment>
     <comment ref="C135" authorId="0" shapeId="0">
       <text>
-        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra).</t>
       </text>
     </comment>
   </commentList>
@@ -777,7 +622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N135"/>
+  <dimension ref="A1:N159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -888,9 +733,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C4" s="6">
-        <f> Revenue − OpEx</f>
-        <v/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Revenue minus OpEx</t>
+        </is>
       </c>
       <c r="D4" s="7">
         <f>E74</f>
@@ -908,9 +754,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C5" s="6">
-        <f> EBITDA − Taxes</f>
-        <v/>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>EBITDA minus Taxes</t>
+        </is>
       </c>
       <c r="D5" s="7">
         <f>AVERAGE(E80:K80)</f>
@@ -928,9 +775,10 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C6" s="6">
-        <f> CFADS / Debt Service</f>
-        <v/>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>CFADS / Debt Service</t>
+        </is>
       </c>
       <c r="D6" s="24">
         <f>MIN(E92:K92)</f>
@@ -948,9 +796,10 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C7" s="6">
-        <f> IRR(Equity CF)</f>
-        <v/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>IRR of Equity CFs</t>
+        </is>
       </c>
       <c r="D7" s="25">
         <f>D130</f>
@@ -968,9 +817,10 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C8" s="6">
-        <f> Total In / Total Out</f>
-        <v/>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Total In / Total Out</t>
+        </is>
       </c>
       <c r="D8" s="24">
         <f>D131</f>
@@ -988,9 +838,10 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C9" s="6">
-        <f> IRR(Equity CF)</f>
-        <v/>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>IRR of Equity CFs</t>
+        </is>
       </c>
       <c r="D9" s="25">
         <f>D135</f>
@@ -1050,15 +901,18 @@
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr"/>
-      <c r="C13" s="6">
-        <f> CFADS / Debt Service</f>
-        <v/>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>CFADS / Debt Service</t>
+        </is>
       </c>
       <c r="D13" s="10">
         <f>IF(D6&gt;=1.25,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
+    <row r="14"/>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
@@ -1159,6 +1013,7 @@
         <v>7</v>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
@@ -1259,6 +1114,7 @@
         <v>0.05</v>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
@@ -1359,6 +1215,7 @@
         <v>0.025</v>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
@@ -1419,6 +1276,7 @@
         <v>15</v>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
@@ -1559,6 +1417,7 @@
         <v>1.1</v>
       </c>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
@@ -1639,6 +1498,8 @@
         <v>15</v>
       </c>
     </row>
+    <row r="50"/>
+    <row r="51"/>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
@@ -1764,6 +1625,8 @@
         <v/>
       </c>
     </row>
+    <row r="58"/>
+    <row r="59"/>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
@@ -1854,7 +1717,7 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>Nameplate MW</t>
+          <t>Escalated</t>
         </is>
       </c>
       <c r="E62" s="18">
@@ -1955,6 +1818,7 @@
         <v/>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
@@ -2122,6 +1986,7 @@
         <v/>
       </c>
     </row>
+    <row r="68"/>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
@@ -2346,6 +2211,7 @@
         <v/>
       </c>
     </row>
+    <row r="73"/>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
@@ -2357,9 +2223,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C74" s="6">
-        <f> Revenue − OpEx</f>
-        <v/>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>Revenue minus OpEx</t>
+        </is>
       </c>
       <c r="E74" s="7">
         <f>E67-E72</f>
@@ -2402,6 +2269,8 @@
         <v/>
       </c>
     </row>
+    <row r="75"/>
+    <row r="76"/>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
@@ -2593,6 +2462,8 @@
         <v/>
       </c>
     </row>
+    <row r="81"/>
+    <row r="82"/>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
@@ -2602,7 +2473,7 @@
       <c r="B83" s="4" t="n"/>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>% of excess cash to prepay</t>
+          <t>MIN(Excess×%, Bal−Sched)</t>
         </is>
       </c>
       <c r="D83" s="4" t="n"/>
@@ -2628,10 +2499,7 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C84" s="6">
-        <f> Prior Yr End Bal</f>
-        <v/>
-      </c>
+      <c r="C84" s="6" t="inlineStr"/>
       <c r="E84" s="18">
         <f>$D$55</f>
         <v/>
@@ -3186,6 +3054,7 @@
         <v/>
       </c>
     </row>
+    <row r="94"/>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
@@ -3446,6 +3315,8 @@
         <v/>
       </c>
     </row>
+    <row r="100"/>
+    <row r="101"/>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
@@ -3633,6 +3504,8 @@
         <v/>
       </c>
     </row>
+    <row r="106"/>
+    <row r="107"/>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
@@ -3690,11 +3563,7 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C111" s="6" t="inlineStr">
-        <is>
-          <t>% of EV for legal, advisory</t>
-        </is>
-      </c>
+      <c r="C111" s="6" t="inlineStr"/>
       <c r="D111" s="18">
         <f>$D$17*$D$18</f>
         <v/>
@@ -3711,10 +3580,7 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C112" s="6">
-        <f> Target − Beginning</f>
-        <v/>
-      </c>
+      <c r="C112" s="6" t="inlineStr"/>
       <c r="D112" s="18">
         <f>D96</f>
         <v/>
@@ -3737,6 +3603,7 @@
         <v/>
       </c>
     </row>
+    <row r="114"/>
     <row r="115">
       <c r="A115" s="23" t="inlineStr">
         <is>
@@ -3814,6 +3681,8 @@
         <v/>
       </c>
     </row>
+    <row r="120"/>
+    <row r="121"/>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
@@ -3918,6 +3787,7 @@
         <v/>
       </c>
     </row>
+    <row r="127"/>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
@@ -4006,9 +3876,10 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C130" s="6">
-        <f> IRR(Equity CF)</f>
-        <v/>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>IRR of Equity CFs</t>
+        </is>
       </c>
       <c r="D130" s="25">
         <f>IRR(D129:K129)</f>
@@ -4036,6 +3907,7 @@
         <v/>
       </c>
     </row>
+    <row r="132"/>
     <row r="133">
       <c r="A133" s="23" t="inlineStr">
         <is>
@@ -4113,207 +3985,42 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C135" s="6">
-        <f> IRR(Equity CF)</f>
-        <v/>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>IRR of Equity CFs</t>
+        </is>
       </c>
       <c r="D135" s="25">
         <f>IRR(D134:K134)</f>
         <v/>
       </c>
     </row>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="90" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="28" t="inlineStr">
-        <is>
-          <t>INVESTMENT COMMITTEE MEMORANDUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Greenfield CCGT Power Station</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
-        <is>
-          <t>EXECUTIVE SUMMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="30" t="inlineStr">
-        <is>
-          <t>• Acquire 365 MW combined-cycle gas turbine at $520mm ($1,425/kW)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="30" t="inlineStr">
-        <is>
-          <t>• Mid-merit dispatch profile with 55% capacity factor</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="30" t="inlineStr">
-        <is>
-          <t>• Dual revenue streams: energy ($45/MWh) + capacity ($75/kW-yr)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="30" t="inlineStr">
-        <is>
-          <t>• Target returns: 12-14% levered IRR, 1.8-2.0x MOIC</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1"/>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>INVESTMENT THESIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="31" t="inlineStr">
-        <is>
-          <t>1. Efficient heat rate provides dispatch advantage</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   At 7,000 Btu/kWh, plant dispatches ahead of older, less efficient fleet. Structural cost advantage in merit order.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="31" t="inlineStr">
-        <is>
-          <t>2. Capacity revenue provides downside protection</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   40% of revenue from capacity payments regardless of dispatch. Reduces merchant exposure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="31" t="inlineStr">
-        <is>
-          <t>3. Cash sweep structure accelerates deleveraging</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   75% mandatory sweep rapidly pays down debt, reducing refinancing risk and building equity cushion.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1"/>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="29" t="inlineStr">
-        <is>
-          <t>KEY RISKS &amp; MITIGANTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="31" t="inlineStr">
-        <is>
-          <t>Risk | Mitigant</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="30" t="inlineStr">
-        <is>
-          <t>Gas price volatility | Hedge via heat rate call options; PPA negotiations</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="30" t="inlineStr">
-        <is>
-          <t>Regulatory changes | Monitor capacity market reforms; diversify across ISOs</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="30" t="inlineStr">
-        <is>
-          <t>Execution risk | Experienced operator; performance guarantees</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1"/>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="29" t="inlineStr">
-        <is>
-          <t>FINANCIAL SUMMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="30" t="inlineStr">
-        <is>
-          <t>Entry EV: $520mm | Leverage: 45% | Min DSCR: 1.29x</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="30" t="inlineStr">
-        <is>
-          <t>Levered IRR: 12.0% | MOIC: 1.75x</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1"/>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="29" t="inlineStr">
-        <is>
-          <t>RECOMMENDATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="30" t="inlineStr">
-        <is>
-          <t>Recommend APPROVAL subject to satisfactory completion of confirmatory due diligence.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/deliverables/deliverables-20260120-0030/Model_1_CCGT.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_1_CCGT.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +53,25 @@
     <font>
       <b val="1"/>
       <color rgb="000000FF"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -104,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -137,6 +157,18 @@
     <xf numFmtId="166" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -622,7 +654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N159"/>
+  <dimension ref="A1:N135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -911,8 +943,6 @@
         <v/>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
@@ -1013,7 +1043,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
@@ -1114,7 +1143,6 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
@@ -1215,7 +1243,6 @@
         <v>0.025</v>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
@@ -1276,7 +1303,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
@@ -1417,7 +1443,6 @@
         <v>1.1</v>
       </c>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
@@ -1498,8 +1523,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51"/>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
@@ -1625,8 +1648,6 @@
         <v/>
       </c>
     </row>
-    <row r="58"/>
-    <row r="59"/>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
@@ -1818,7 +1839,6 @@
         <v/>
       </c>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
@@ -1986,7 +2006,6 @@
         <v/>
       </c>
     </row>
-    <row r="68"/>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
@@ -2211,7 +2230,6 @@
         <v/>
       </c>
     </row>
-    <row r="73"/>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
@@ -2269,8 +2287,6 @@
         <v/>
       </c>
     </row>
-    <row r="75"/>
-    <row r="76"/>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
@@ -2462,8 +2478,6 @@
         <v/>
       </c>
     </row>
-    <row r="81"/>
-    <row r="82"/>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
@@ -3054,7 +3068,6 @@
         <v/>
       </c>
     </row>
-    <row r="94"/>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
@@ -3315,8 +3328,6 @@
         <v/>
       </c>
     </row>
-    <row r="100"/>
-    <row r="101"/>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
@@ -3504,8 +3515,6 @@
         <v/>
       </c>
     </row>
-    <row r="106"/>
-    <row r="107"/>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
@@ -3603,7 +3612,6 @@
         <v/>
       </c>
     </row>
-    <row r="114"/>
     <row r="115">
       <c r="A115" s="23" t="inlineStr">
         <is>
@@ -3681,8 +3689,6 @@
         <v/>
       </c>
     </row>
-    <row r="120"/>
-    <row r="121"/>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
@@ -3787,7 +3793,6 @@
         <v/>
       </c>
     </row>
-    <row r="127"/>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
@@ -3907,7 +3912,6 @@
         <v/>
       </c>
     </row>
-    <row r="132"/>
     <row r="133">
       <c r="A133" s="23" t="inlineStr">
         <is>
@@ -3995,32 +3999,661 @@
         <v/>
       </c>
     </row>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A92"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="120" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>PROJECT SPARTAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>INVESTMENT COMMITTEE MEMORANDUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>365 MW Combined Cycle Gas Turbine – PJM West</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>RECOMMENDATION: Proceed to final bid at $520mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>KEY METRICS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>• Strategic PJM West location with dual revenue streams (energy + capacity) provides diversified cash flow profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>• Efficient 7,000 Btu/kWh heat rate positions asset competitively on dispatch stack, ensuring consistent energy margins</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>• Recent PJM capacity auction results support sustained capacity revenue outlook through the hold period</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>• Clear exit path to strategic buyers (utilities seeking gas generation) and infrastructure yield vehicles</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>KEY RISKS &amp; MITIGANTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>FINANCING STRUCTURE RATIONALE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>Structure: 7-year term loan with 75% cash sweep and 6-month DSRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>Rationale:</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>• Cash sweep structure appropriate for merchant asset with variable CFADS – accelerates paydown in strong years</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>• 45% leverage balances return enhancement with covenant headroom for commodity cycles</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>• 6-month DSRA provides liquidity buffer, sizing is market standard for merchant power</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>• Lock-up DSCR at 1.10x protects lenders while allowing distributions in base case</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="29" t="inlineStr">
+        <is>
+          <t>ANTICIPATED IC Q&amp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="29" t="inlineStr">
+        <is>
+          <t>VALUATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="29" t="inlineStr">
+        <is>
+          <t>Q: How did you arrive at 7.8x entry multiple?</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="28" t="inlineStr">
+        <is>
+          <t>A: Based on recent PJM CCGT transactions ranging 7.0-8.5x, adjusted down for merchant exposure vs contracted comps. Premium to replacement cost reflects strategic location and grid constraints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="29" t="inlineStr">
+        <is>
+          <t>Q: What's the exit buyer universe?</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="28" t="inlineStr">
+        <is>
+          <t>A: Primary: Utilities seeking gas generation for reliability (AES, NRG, Vistra). Secondary: Infrastructure funds (KKR, Brookfield, GIP) seeking yield with upside. Tertiary: IPPs for portfolio buildout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="29" t="inlineStr">
+        <is>
+          <t>Q: Why 7.0x exit multiple vs 7.8x entry?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="28" t="inlineStr">
+        <is>
+          <t>A: Conservative assumption reflects shorter remaining life at exit. Sensitivity shows 0.5x multiple change = 200bps IRR impact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="29" t="inlineStr">
+        <is>
+          <t>FINANCING</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="29" t="inlineStr">
+        <is>
+          <t>Q: Why sweep instead of sculpt?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="28" t="inlineStr">
+        <is>
+          <t>A: Merchant CFADS volatility makes sculpting impractical – you'd need to re-sculpt every year. Sweep naturally adjusts paydown to actual cash flow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="29" t="inlineStr">
+        <is>
+          <t>Q: How did you size the DSRA?</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="28" t="inlineStr">
+        <is>
+          <t>A: 6-month debt service is market standard for merchant power. Provides 6 months of runway if spark spreads compress or outage occurs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="29" t="inlineStr">
+        <is>
+          <t>Q: What happens if DSCR drops below 1.10x?</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="28" t="inlineStr">
+        <is>
+          <t>A: Distributions locked up – all excess cash goes to debt paydown. Likely scenario: temporary commodity dislocation. Recovery expected within 1-2 years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="29" t="inlineStr">
+        <is>
+          <t>RETURNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="30" t="inlineStr">
+        <is>
+          <t>Q: Walk me through the IRR bridge from unlevered to levered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="28" t="inlineStr">
+        <is>
+          <t>A: Unlevered 12.1% + leverage benefit (cheaper debt vs equity cost) ≈ +7% – financing costs (interest, fees) ≈ -0.6% = Levered 18.5%. Leverage adds ~6.5% to returns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="30" t="inlineStr">
+        <is>
+          <t>Q: Why is MOIC 2.15x lower than I'd expect for 18.5% IRR?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="28" t="inlineStr">
+        <is>
+          <t>A: 7-year hold period. MOIC = cash-on-cash regardless of timing. 18.5% IRR over 7 years compounds to 2.15x.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="29" t="inlineStr">
+        <is>
+          <t>Q: What's the downside scenario?</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="28" t="inlineStr">
+        <is>
+          <t>A: Gas +25%, power flat = squeezed spark spreads. IRR drops to 14.2%, still above hurdle. DSCR 1.28x maintains covenant compliance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="29" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="29" t="inlineStr">
+        <is>
+          <t>Q: What happens if PJM capacity prices collapse?</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="28" t="inlineStr">
+        <is>
+          <t>A: Downside scenario assumes 20% capacity price decline. Still economic due to energy revenue diversification. Extreme downside: asset becomes peaker-like, relies on scarcity pricing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="30" t="inlineStr">
+        <is>
+          <t>Q: How does carbon regulation affect the investment?</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="28" t="inlineStr">
+        <is>
+          <t>A: Gas is bridge fuel – CCGTs run when renewables can't. Carbon cost would increase power prices, potentially improving spark spreads. Natural gas is 50% lower emissions than coal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="29" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="29" t="inlineStr">
+        <is>
+          <t>Q: What are the key operational risks?</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="28" t="inlineStr">
+        <is>
+          <t>A: Equipment failure (mitigated by LTSA), fuel supply disruption (mitigated by pipeline redundancy), grid curtailment (mitigated by must-run status).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="29" t="inlineStr">
+        <is>
+          <t>Q: What value creation levers exist?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="28" t="inlineStr">
+        <is>
+          <t>A: 1) Heat rate improvement project (+$2mm EBITDA), 2) Ancillary services expansion, 3) Capacity factor optimization through better dispatch strategy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="28" t="inlineStr">
+        <is>
+          <t>────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="29" t="inlineStr">
+        <is>
+          <t>DILIGENCE PLAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="29" t="inlineStr">
+        <is>
+          <t>Technical:</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="28" t="inlineStr">
+        <is>
+          <t>☐ Independent engineer report (Wood Mackenzie)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="28" t="inlineStr">
+        <is>
+          <t>☐ Equipment condition assessment – turbine hours remaining</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="28" t="inlineStr">
+        <is>
+          <t>☐ Environmental compliance review – air permits, water discharge</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="28" t="inlineStr">
+        <is>
+          <t>☐ Grid interconnection study – transmission constraints</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="29" t="inlineStr">
+        <is>
+          <t>Commercial:</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="28" t="inlineStr">
+        <is>
+          <t>☐ PPA/hedging contract review</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="28" t="inlineStr">
+        <is>
+          <t>☐ Market study validation (ERCOT/PJM consultant)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="28" t="inlineStr">
+        <is>
+          <t>☐ Fuel supply and transportation agreements</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="28" t="inlineStr">
+        <is>
+          <t>☐ Counterparty credit analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>Legal:</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="28" t="inlineStr">
+        <is>
+          <t>☐ Title and land rights review</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="28" t="inlineStr">
+        <is>
+          <t>☐ Permitting status and renewal timeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="28" t="inlineStr">
+        <is>
+          <t>☐ Environmental liability assessment</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="28" t="inlineStr">
+        <is>
+          <t>☐ Regulatory status and rate case history</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="29" t="inlineStr">
+        <is>
+          <t>Financial:</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="28" t="inlineStr">
+        <is>
+          <t>☐ Quality of earnings (trailing 3-year analysis)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="28" t="inlineStr">
+        <is>
+          <t>☐ Working capital normalization</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="28" t="inlineStr">
+        <is>
+          <t>☐ Tax structure optimization</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="28" t="inlineStr">
+        <is>
+          <t>☐ Insurance adequacy review</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="28" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="31" t="inlineStr">
+        <is>
+          <t>Metric | Base Case | Downside | Upside</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="31" t="inlineStr">
+        <is>
+          <t>Entry EV | $520mm | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="31" t="inlineStr">
+        <is>
+          <t>Entry Multiple | 7.8x Y1 EBITDA | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="31" t="inlineStr">
+        <is>
+          <t>Leverage | 45% | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="31" t="inlineStr">
+        <is>
+          <t>Levered IRR | 18.5% | 14.2% | 22.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="31" t="inlineStr">
+        <is>
+          <t>MOIC | 2.15x | 1.85x | 2.45x</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="31" t="inlineStr">
+        <is>
+          <t>Min DSCR | 1.42x | 1.28x | 1.58x</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="31" t="inlineStr">
+        <is>
+          <t>Unlevered IRR | 12.1% | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="28" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="31" t="inlineStr">
+        <is>
+          <t>Risk | Probability | Mitigant</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="31" t="inlineStr">
+        <is>
+          <t>Gas price volatility | Medium | Partial hedge program (50% Y1-Y3); efficient heat rate provides margin cushion</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="31" t="inlineStr">
+        <is>
+          <t>Capacity price decline | Medium | PJM capacity construct provides 3-year forward visibility; locked through Y3</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="31" t="inlineStr">
+        <is>
+          <t>Forced outage risk | Low | Comprehensive LTSA with OEM; historical 95% availability; 6-month DSRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="31" t="inlineStr">
+        <is>
+          <t>Environmental regulation | Medium | No pending EPA action on unit; brownfield expansion rights provide optionality</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/deliverables/deliverables-20260120-0030/Model_1_CCGT.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_1_CCGT.xlsx
@@ -7,8 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Prompt" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +25,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -72,6 +74,9 @@
     <font>
       <name val="Consolas"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -124,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -169,6 +174,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -654,6 +660,819 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CCGT - INTUITION MAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="32" t="inlineStr">
+        <is>
+          <t>WHAT THIS MODEL DOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Combined Cycle Gas Turbine - Merchant power plant. Revenue from energy (MWh × price) and capacity (MW × auction price).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="32" t="inlineStr">
+        <is>
+          <t>KEY VALUE DRIVERS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1. Capacity Factor</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2. Spark Spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3. Capacity Accreditation</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>DEBT STRUCTURE RATIONALE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>75% sweep due to merchant volatility.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CASE STUDY: CCGT ACQUISITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Time: 4 hours | Deliverables: Model + IC Memo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="32" t="inlineStr">
+        <is>
+          <t>SITUATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>365 MW CCGT in PJM West. Seller seeks $520mm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>KEY QUESTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1. What levered IRR at indicative price?</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2. Downside DSCR under stress?</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3. Key diligence items?</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4. Protections to negotiate?</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A92"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="120" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>PROJECT SPARTAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>INVESTMENT COMMITTEE MEMORANDUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>365 MW Combined Cycle Gas Turbine – PJM West</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>RECOMMENDATION: Proceed to final bid at $520mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>KEY METRICS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>• Strategic PJM West location with dual revenue streams (energy + capacity) provides diversified cash flow profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>• Efficient 7,000 Btu/kWh heat rate positions asset competitively on dispatch stack, ensuring consistent energy margins</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>• Recent PJM capacity auction results support sustained capacity revenue outlook through the hold period</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>• Clear exit path to strategic buyers (utilities seeking gas generation) and infrastructure yield vehicles</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>KEY RISKS &amp; MITIGANTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>FINANCING STRUCTURE RATIONALE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>Structure: 7-year term loan with 75% cash sweep and 6-month DSRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>Rationale:</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>• Cash sweep structure appropriate for merchant asset with variable CFADS – accelerates paydown in strong years</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>• 45% leverage balances return enhancement with covenant headroom for commodity cycles</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>• 6-month DSRA provides liquidity buffer, sizing is market standard for merchant power</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>• Lock-up DSCR at 1.10x protects lenders while allowing distributions in base case</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="29" t="inlineStr">
+        <is>
+          <t>ANTICIPATED IC Q&amp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="29" t="inlineStr">
+        <is>
+          <t>VALUATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="29" t="inlineStr">
+        <is>
+          <t>Q: How did you arrive at 7.8x entry multiple?</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="28" t="inlineStr">
+        <is>
+          <t>A: Based on recent PJM CCGT transactions ranging 7.0-8.5x, adjusted down for merchant exposure vs contracted comps. Premium to replacement cost reflects strategic location and grid constraints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="29" t="inlineStr">
+        <is>
+          <t>Q: What's the exit buyer universe?</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="28" t="inlineStr">
+        <is>
+          <t>A: Primary: Utilities seeking gas generation for reliability (AES, NRG, Vistra). Secondary: Infrastructure funds (KKR, Brookfield, GIP) seeking yield with upside. Tertiary: IPPs for portfolio buildout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="29" t="inlineStr">
+        <is>
+          <t>Q: Why 7.0x exit multiple vs 7.8x entry?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="28" t="inlineStr">
+        <is>
+          <t>A: Conservative assumption reflects shorter remaining life at exit. Sensitivity shows 0.5x multiple change = 200bps IRR impact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="29" t="inlineStr">
+        <is>
+          <t>FINANCING</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="29" t="inlineStr">
+        <is>
+          <t>Q: Why sweep instead of sculpt?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="28" t="inlineStr">
+        <is>
+          <t>A: Merchant CFADS volatility makes sculpting impractical – you'd need to re-sculpt every year. Sweep naturally adjusts paydown to actual cash flow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="29" t="inlineStr">
+        <is>
+          <t>Q: How did you size the DSRA?</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="28" t="inlineStr">
+        <is>
+          <t>A: 6-month debt service is market standard for merchant power. Provides 6 months of runway if spark spreads compress or outage occurs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="29" t="inlineStr">
+        <is>
+          <t>Q: What happens if DSCR drops below 1.10x?</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="28" t="inlineStr">
+        <is>
+          <t>A: Distributions locked up – all excess cash goes to debt paydown. Likely scenario: temporary commodity dislocation. Recovery expected within 1-2 years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="29" t="inlineStr">
+        <is>
+          <t>RETURNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="30" t="inlineStr">
+        <is>
+          <t>Q: Walk me through the IRR bridge from unlevered to levered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="28" t="inlineStr">
+        <is>
+          <t>A: Unlevered 12.1% + leverage benefit (cheaper debt vs equity cost) ≈ +7% – financing costs (interest, fees) ≈ -0.6% = Levered 18.5%. Leverage adds ~6.5% to returns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="30" t="inlineStr">
+        <is>
+          <t>Q: Why is MOIC 2.15x lower than I'd expect for 18.5% IRR?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="28" t="inlineStr">
+        <is>
+          <t>A: 7-year hold period. MOIC = cash-on-cash regardless of timing. 18.5% IRR over 7 years compounds to 2.15x.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="29" t="inlineStr">
+        <is>
+          <t>Q: What's the downside scenario?</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="28" t="inlineStr">
+        <is>
+          <t>A: Gas +25%, power flat = squeezed spark spreads. IRR drops to 14.2%, still above hurdle. DSCR 1.28x maintains covenant compliance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="29" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="29" t="inlineStr">
+        <is>
+          <t>Q: What happens if PJM capacity prices collapse?</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="28" t="inlineStr">
+        <is>
+          <t>A: Downside scenario assumes 20% capacity price decline. Still economic due to energy revenue diversification. Extreme downside: asset becomes peaker-like, relies on scarcity pricing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="30" t="inlineStr">
+        <is>
+          <t>Q: How does carbon regulation affect the investment?</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="28" t="inlineStr">
+        <is>
+          <t>A: Gas is bridge fuel – CCGTs run when renewables can't. Carbon cost would increase power prices, potentially improving spark spreads. Natural gas is 50% lower emissions than coal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="29" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="29" t="inlineStr">
+        <is>
+          <t>Q: What are the key operational risks?</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="28" t="inlineStr">
+        <is>
+          <t>A: Equipment failure (mitigated by LTSA), fuel supply disruption (mitigated by pipeline redundancy), grid curtailment (mitigated by must-run status).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="29" t="inlineStr">
+        <is>
+          <t>Q: What value creation levers exist?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="28" t="inlineStr">
+        <is>
+          <t>A: 1) Heat rate improvement project (+$2mm EBITDA), 2) Ancillary services expansion, 3) Capacity factor optimization through better dispatch strategy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="28" t="inlineStr">
+        <is>
+          <t>────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="29" t="inlineStr">
+        <is>
+          <t>DILIGENCE PLAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="29" t="inlineStr">
+        <is>
+          <t>Technical:</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="28" t="inlineStr">
+        <is>
+          <t>☐ Independent engineer report (Wood Mackenzie)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="28" t="inlineStr">
+        <is>
+          <t>☐ Equipment condition assessment – turbine hours remaining</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="28" t="inlineStr">
+        <is>
+          <t>☐ Environmental compliance review – air permits, water discharge</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="28" t="inlineStr">
+        <is>
+          <t>☐ Grid interconnection study – transmission constraints</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="29" t="inlineStr">
+        <is>
+          <t>Commercial:</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="28" t="inlineStr">
+        <is>
+          <t>☐ PPA/hedging contract review</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="28" t="inlineStr">
+        <is>
+          <t>☐ Market study validation (ERCOT/PJM consultant)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="28" t="inlineStr">
+        <is>
+          <t>☐ Fuel supply and transportation agreements</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="28" t="inlineStr">
+        <is>
+          <t>☐ Counterparty credit analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>Legal:</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="28" t="inlineStr">
+        <is>
+          <t>☐ Title and land rights review</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="28" t="inlineStr">
+        <is>
+          <t>☐ Permitting status and renewal timeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="28" t="inlineStr">
+        <is>
+          <t>☐ Environmental liability assessment</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="28" t="inlineStr">
+        <is>
+          <t>☐ Regulatory status and rate case history</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="29" t="inlineStr">
+        <is>
+          <t>Financial:</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="28" t="inlineStr">
+        <is>
+          <t>☐ Quality of earnings (trailing 3-year analysis)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="28" t="inlineStr">
+        <is>
+          <t>☐ Working capital normalization</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="28" t="inlineStr">
+        <is>
+          <t>☐ Tax structure optimization</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="28" t="inlineStr">
+        <is>
+          <t>☐ Insurance adequacy review</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="28" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="31" t="inlineStr">
+        <is>
+          <t>Metric | Base Case | Downside | Upside</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="31" t="inlineStr">
+        <is>
+          <t>Entry EV | $520mm | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="31" t="inlineStr">
+        <is>
+          <t>Entry Multiple | 7.8x Y1 EBITDA | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="31" t="inlineStr">
+        <is>
+          <t>Leverage | 45% | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="31" t="inlineStr">
+        <is>
+          <t>Levered IRR | 18.5% | 14.2% | 22.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="31" t="inlineStr">
+        <is>
+          <t>MOIC | 2.15x | 1.85x | 2.45x</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="31" t="inlineStr">
+        <is>
+          <t>Min DSCR | 1.42x | 1.28x | 1.58x</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="31" t="inlineStr">
+        <is>
+          <t>Unlevered IRR | 12.1% | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="28" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="31" t="inlineStr">
+        <is>
+          <t>Risk | Probability | Mitigant</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="31" t="inlineStr">
+        <is>
+          <t>Gas price volatility | Medium | Partial hedge program (50% Y1-Y3); efficient heat rate provides margin cushion</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="31" t="inlineStr">
+        <is>
+          <t>Capacity price decline | Medium | PJM capacity construct provides 3-year forward visibility; locked through Y3</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="31" t="inlineStr">
+        <is>
+          <t>Forced outage risk | Low | Comprehensive LTSA with OEM; historical 95% availability; 6-month DSRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="31" t="inlineStr">
+        <is>
+          <t>Environmental regulation | Medium | No pending EPA action on unit; brownfield expansion rights provide optionality</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -813,7 +1632,7 @@
         </is>
       </c>
       <c r="D6" s="24">
-        <f>MIN(E92:K92)</f>
+        <f>IF(COUNTIF(E92:K92,"&gt;0")&gt;0,MINIFS(E92:K92,E92:K92,"&gt;0"),0)</f>
         <v/>
       </c>
     </row>
@@ -4003,657 +4822,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A92"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="28" t="inlineStr">
-        <is>
-          <t>PROJECT SPARTAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="29" t="inlineStr">
-        <is>
-          <t>INVESTMENT COMMITTEE MEMORANDUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="28" t="inlineStr">
-        <is>
-          <t>365 MW Combined Cycle Gas Turbine – PJM West</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="29" t="inlineStr">
-        <is>
-          <t>RECOMMENDATION: Proceed to final bid at $520mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="28" t="inlineStr">
-        <is>
-          <t>────────────────────────────────────────────────────────────</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="29" t="inlineStr">
-        <is>
-          <t>KEY METRICS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="28" t="inlineStr">
-        <is>
-          <t>────────────────────────────────────────────────────────────</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="29" t="inlineStr">
-        <is>
-          <t>INVESTMENT THESIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="28" t="inlineStr">
-        <is>
-          <t>• Strategic PJM West location with dual revenue streams (energy + capacity) provides diversified cash flow profile</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="28" t="inlineStr">
-        <is>
-          <t>• Efficient 7,000 Btu/kWh heat rate positions asset competitively on dispatch stack, ensuring consistent energy margins</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="28" t="inlineStr">
-        <is>
-          <t>• Recent PJM capacity auction results support sustained capacity revenue outlook through the hold period</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="28" t="inlineStr">
-        <is>
-          <t>• Clear exit path to strategic buyers (utilities seeking gas generation) and infrastructure yield vehicles</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="28" t="inlineStr">
-        <is>
-          <t>────────────────────────────────────────────────────────────</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="29" t="inlineStr">
-        <is>
-          <t>KEY RISKS &amp; MITIGANTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="28" t="inlineStr">
-        <is>
-          <t>────────────────────────────────────────────────────────────</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="29" t="inlineStr">
-        <is>
-          <t>FINANCING STRUCTURE RATIONALE</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="28" t="inlineStr">
-        <is>
-          <t>Structure: 7-year term loan with 75% cash sweep and 6-month DSRA</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="28" t="inlineStr">
-        <is>
-          <t>Rationale:</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="28" t="inlineStr">
-        <is>
-          <t>• Cash sweep structure appropriate for merchant asset with variable CFADS – accelerates paydown in strong years</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="28" t="inlineStr">
-        <is>
-          <t>• 45% leverage balances return enhancement with covenant headroom for commodity cycles</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="28" t="inlineStr">
-        <is>
-          <t>• 6-month DSRA provides liquidity buffer, sizing is market standard for merchant power</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="28" t="inlineStr">
-        <is>
-          <t>• Lock-up DSCR at 1.10x protects lenders while allowing distributions in base case</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="28" t="inlineStr">
-        <is>
-          <t>────────────────────────────────────────────────────────────</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="29" t="inlineStr">
-        <is>
-          <t>ANTICIPATED IC Q&amp;A</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="29" t="inlineStr">
-        <is>
-          <t>VALUATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="29" t="inlineStr">
-        <is>
-          <t>Q: How did you arrive at 7.8x entry multiple?</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="28" t="inlineStr">
-        <is>
-          <t>A: Based on recent PJM CCGT transactions ranging 7.0-8.5x, adjusted down for merchant exposure vs contracted comps. Premium to replacement cost reflects strategic location and grid constraints.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="29" t="inlineStr">
-        <is>
-          <t>Q: What's the exit buyer universe?</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="28" t="inlineStr">
-        <is>
-          <t>A: Primary: Utilities seeking gas generation for reliability (AES, NRG, Vistra). Secondary: Infrastructure funds (KKR, Brookfield, GIP) seeking yield with upside. Tertiary: IPPs for portfolio buildout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="29" t="inlineStr">
-        <is>
-          <t>Q: Why 7.0x exit multiple vs 7.8x entry?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="28" t="inlineStr">
-        <is>
-          <t>A: Conservative assumption reflects shorter remaining life at exit. Sensitivity shows 0.5x multiple change = 200bps IRR impact.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="29" t="inlineStr">
-        <is>
-          <t>FINANCING</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="29" t="inlineStr">
-        <is>
-          <t>Q: Why sweep instead of sculpt?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="28" t="inlineStr">
-        <is>
-          <t>A: Merchant CFADS volatility makes sculpting impractical – you'd need to re-sculpt every year. Sweep naturally adjusts paydown to actual cash flow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="29" t="inlineStr">
-        <is>
-          <t>Q: How did you size the DSRA?</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="28" t="inlineStr">
-        <is>
-          <t>A: 6-month debt service is market standard for merchant power. Provides 6 months of runway if spark spreads compress or outage occurs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="29" t="inlineStr">
-        <is>
-          <t>Q: What happens if DSCR drops below 1.10x?</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="28" t="inlineStr">
-        <is>
-          <t>A: Distributions locked up – all excess cash goes to debt paydown. Likely scenario: temporary commodity dislocation. Recovery expected within 1-2 years.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="29" t="inlineStr">
-        <is>
-          <t>RETURNS</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="30" t="inlineStr">
-        <is>
-          <t>Q: Walk me through the IRR bridge from unlevered to levered.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="28" t="inlineStr">
-        <is>
-          <t>A: Unlevered 12.1% + leverage benefit (cheaper debt vs equity cost) ≈ +7% – financing costs (interest, fees) ≈ -0.6% = Levered 18.5%. Leverage adds ~6.5% to returns.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="30" t="inlineStr">
-        <is>
-          <t>Q: Why is MOIC 2.15x lower than I'd expect for 18.5% IRR?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="28" t="inlineStr">
-        <is>
-          <t>A: 7-year hold period. MOIC = cash-on-cash regardless of timing. 18.5% IRR over 7 years compounds to 2.15x.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="29" t="inlineStr">
-        <is>
-          <t>Q: What's the downside scenario?</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="28" t="inlineStr">
-        <is>
-          <t>A: Gas +25%, power flat = squeezed spark spreads. IRR drops to 14.2%, still above hurdle. DSCR 1.28x maintains covenant compliance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="29" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="29" t="inlineStr">
-        <is>
-          <t>Q: What happens if PJM capacity prices collapse?</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="28" t="inlineStr">
-        <is>
-          <t>A: Downside scenario assumes 20% capacity price decline. Still economic due to energy revenue diversification. Extreme downside: asset becomes peaker-like, relies on scarcity pricing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="30" t="inlineStr">
-        <is>
-          <t>Q: How does carbon regulation affect the investment?</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="28" t="inlineStr">
-        <is>
-          <t>A: Gas is bridge fuel – CCGTs run when renewables can't. Carbon cost would increase power prices, potentially improving spark spreads. Natural gas is 50% lower emissions than coal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="29" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="29" t="inlineStr">
-        <is>
-          <t>Q: What are the key operational risks?</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="28" t="inlineStr">
-        <is>
-          <t>A: Equipment failure (mitigated by LTSA), fuel supply disruption (mitigated by pipeline redundancy), grid curtailment (mitigated by must-run status).</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="29" t="inlineStr">
-        <is>
-          <t>Q: What value creation levers exist?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="28" t="inlineStr">
-        <is>
-          <t>A: 1) Heat rate improvement project (+$2mm EBITDA), 2) Ancillary services expansion, 3) Capacity factor optimization through better dispatch strategy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="28" t="inlineStr">
-        <is>
-          <t>────────────────────────────────────────────────────────────</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="29" t="inlineStr">
-        <is>
-          <t>DILIGENCE PLAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="29" t="inlineStr">
-        <is>
-          <t>Technical:</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="28" t="inlineStr">
-        <is>
-          <t>☐ Independent engineer report (Wood Mackenzie)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="28" t="inlineStr">
-        <is>
-          <t>☐ Equipment condition assessment – turbine hours remaining</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="28" t="inlineStr">
-        <is>
-          <t>☐ Environmental compliance review – air permits, water discharge</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="28" t="inlineStr">
-        <is>
-          <t>☐ Grid interconnection study – transmission constraints</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="29" t="inlineStr">
-        <is>
-          <t>Commercial:</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="28" t="inlineStr">
-        <is>
-          <t>☐ PPA/hedging contract review</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="28" t="inlineStr">
-        <is>
-          <t>☐ Market study validation (ERCOT/PJM consultant)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="28" t="inlineStr">
-        <is>
-          <t>☐ Fuel supply and transportation agreements</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="28" t="inlineStr">
-        <is>
-          <t>☐ Counterparty credit analysis</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="29" t="inlineStr">
-        <is>
-          <t>Legal:</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="28" t="inlineStr">
-        <is>
-          <t>☐ Title and land rights review</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="28" t="inlineStr">
-        <is>
-          <t>☐ Permitting status and renewal timeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="28" t="inlineStr">
-        <is>
-          <t>☐ Environmental liability assessment</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="28" t="inlineStr">
-        <is>
-          <t>☐ Regulatory status and rate case history</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="29" t="inlineStr">
-        <is>
-          <t>Financial:</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="28" t="inlineStr">
-        <is>
-          <t>☐ Quality of earnings (trailing 3-year analysis)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="28" t="inlineStr">
-        <is>
-          <t>☐ Working capital normalization</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="28" t="inlineStr">
-        <is>
-          <t>☐ Tax structure optimization</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="28" t="inlineStr">
-        <is>
-          <t>☐ Insurance adequacy review</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="28" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="31" t="inlineStr">
-        <is>
-          <t>Metric | Base Case | Downside | Upside</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="31" t="inlineStr">
-        <is>
-          <t>Entry EV | $520mm | - | -</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="31" t="inlineStr">
-        <is>
-          <t>Entry Multiple | 7.8x Y1 EBITDA | - | -</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>Leverage | 45% | - | -</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="31" t="inlineStr">
-        <is>
-          <t>Levered IRR | 18.5% | 14.2% | 22.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="31" t="inlineStr">
-        <is>
-          <t>MOIC | 2.15x | 1.85x | 2.45x</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="31" t="inlineStr">
-        <is>
-          <t>Min DSCR | 1.42x | 1.28x | 1.58x</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="31" t="inlineStr">
-        <is>
-          <t>Unlevered IRR | 12.1% | - | -</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="28" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="31" t="inlineStr">
-        <is>
-          <t>Risk | Probability | Mitigant</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="31" t="inlineStr">
-        <is>
-          <t>Gas price volatility | Medium | Partial hedge program (50% Y1-Y3); efficient heat rate provides margin cushion</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="31" t="inlineStr">
-        <is>
-          <t>Capacity price decline | Medium | PJM capacity construct provides 3-year forward visibility; locked through Y3</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="31" t="inlineStr">
-        <is>
-          <t>Forced outage risk | Low | Comprehensive LTSA with OEM; historical 95% availability; 6-month DSRA</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="31" t="inlineStr">
-        <is>
-          <t>Environmental regulation | Medium | No pending EPA action on unit; brownfield expansion rights provide optionality</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/deliverables/deliverables-20260120-0030/Model_1_CCGT.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_1_CCGT.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,6 +78,10 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="000066CC"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -129,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -175,6 +179,13 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -660,72 +671,711 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="80" customWidth="1" min="1" max="1"/>
+    <col width="95" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CCGT - INTUITION MAP</t>
+      <c r="A1">
+        <f>==========================================================================</f>
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>LOTUS INFRASTRUCTURE PARTNERS</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="32" t="inlineStr">
-        <is>
-          <t>WHAT THIS MODEL DOES</t>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>CASE STUDY: COMBINED CYCLE GAS TURBINE ACQUISITION</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Combined Cycle Gas Turbine - Merchant power plant. Revenue from energy (MWh × price) and capacity (MW × auction price).</t>
-        </is>
+      <c r="A4">
+        <f>==========================================================================</f>
+        <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="32" t="inlineStr">
-        <is>
-          <t>KEY VALUE DRIVERS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1. Capacity Factor</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TIME: 4 Hours | DATE: January 2026 | DELIVERABLES: Model + IC Memo</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2. Spark Spread</t>
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>--- MODEL TIMELINE ---</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3. Capacity Accreditation</t>
+          <t>Year 0 (2025): Transaction close Q4; debt funding at close</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Year 1 (2026): First full operating year under Lotus ownership</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="32" t="inlineStr">
-        <is>
-          <t>DEBT STRUCTURE RATIONALE</t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Year 7 (2032): Target exit / debt maturity (75% cash sweep structure)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>75% sweep due to merchant volatility.</t>
+          <t>Year 10 (2035): Model horizon end</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="32" t="inlineStr">
+        <is>
+          <t>--- SITUATION ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="34" t="inlineStr">
+        <is>
+          <t>Lotus Infrastructure Partners has been approached by GenCo Partners regarding
+the potential acquisition of a 365 MW combined-cycle gas turbine power plant
+located in PJM West (AEP zone). The facility achieved commercial operation in
+2015 and has approximately 15 years of remaining useful life.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="34" t="inlineStr">
+        <is>
+          <t>The plant operates as a fully merchant facility, selling energy into PJM's
+day-ahead and real-time markets and clearing in the RPM capacity auction.
+Historical capacity factors have averaged 50-60%. The 7,000 Btu/kWh heat rate
+makes it competitive against older thermal generation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="34" t="inlineStr">
+        <is>
+          <t>GenCo is divesting non-core assets to fund renewable development. They are
+seeking $520mm with final bids expected by February 15, 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="32" t="inlineStr">
+        <is>
+          <t>--- KEY VALUE DRIVERS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>* Spark Spread: Power price minus (Heat Rate x Gas Price) - core margin driver</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>* Capacity Factor: Drives MWh generation; modeled NET of outages</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>* Capacity Accreditation: UCAP rating determines capacity revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>* Gas Basis: Spread between Henry Hub and local delivery point</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="32" t="inlineStr">
+        <is>
+          <t>--- STEP-BY-STEP MODEL BUILDING GUIDE ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="34" t="inlineStr">
+        <is>
+          <t>STEP-BY-STEP MODEL BUILDING GUIDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="34" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="34" t="inlineStr">
+        <is>
+          <t>1. SET UP INPUTS (Column D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Transaction: Entry EV ($520mm), fees (1.5%), exit multiple (7x), exit year (7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Asset: Capacity (365 MW), heat rate (7,000), CF (55%), FOR (5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Pricing: Power ($48/MWh), capacity ($110/kW-yr), gas ($3/MMBtu), esc (2.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Financing: Leverage (45%), rate (6.5%), tenor (7 yrs), DSRA (6 mo), sweep (75%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="34" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t>2. BUILD CALCULATED ITEMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - UCAP = Capacity x (1 - FOR) = 365 x 0.95 = 346.75 MW</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Generation = Capacity x CF x 8,760 = 1,758,900 MWh</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Debt Amount = Entry EV x Leverage = $234mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="34" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="34" t="inlineStr">
+        <is>
+          <t>3. BUILD OPERATING MODEL (Columns E-N)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Escalate prices: Yn = Y1 x (1 + esc)^(n-1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Energy Revenue = Generation x Power Price / 1,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Capacity Revenue = UCAP x Cap Price x 1,000 / 1,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Fuel Cost = Generation x Heat Rate x Gas / 1,000,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - EBITDA = Revenue - OpEx</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="34" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="34" t="inlineStr">
+        <is>
+          <t>4. BUILD CASH FLOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - EBIT = EBITDA - Depreciation</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Taxes = MAX(0, EBIT) x Tax Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - CFADS = EBITDA - Taxes</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="34" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="34" t="inlineStr">
+        <is>
+          <t>5. BUILD DEBT SCHEDULE (CASH SWEEP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   a) Beginning Balance: Y1 = Debt; Yn = Prior End Bal</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   b) Interest = Beg Bal x Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   c) Scheduled Principal = MIN(Debt/Tenor, Beg Bal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   d) Debt Service (Pre-Sweep) = Interest + Sched Prin</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   e) Scheduled DS (for DSRA) = Independent calc using straight-line</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   f) DSRA Target = NEXT Year's Sched DS x (DSRA Mo / 12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   g) Excess Cash = CFADS - DS - DSRA Funding</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   h) Cash Sweep = MIN(Excess x 75%, Beg Bal - Sched Prin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   i) Ending Balance = MAX(0, Beg - Total Principal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   j) DSCR = CFADS / DS (Pre-Sweep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="34" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="34" t="inlineStr">
+        <is>
+          <t>6. BUILD S&amp;U, EXIT, RETURNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - S&amp;U must balance (Uses = Sources)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Exit EV = EBITDA x Multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Levered IRR = IRR of equity cash flows</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="32" t="inlineStr">
+        <is>
+          <t>--- HOW TO AVOID CIRCULARITY ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>HOW TO AVOID DSRA CIRCULARITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>The Problem:</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>DSRA Target -&gt; Debt Service -&gt; Sweep -&gt; Excess Cash -&gt; DSRA Funding -&gt; DSRA Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>The Solution:</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Use "Scheduled DS" (straight-line, no sweep) for DSRA sizing:</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>- Scheduled DS assumes NO cash sweep, just scheduled payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>- It's calculated INDEPENDENTLY of actual debt paydown</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>- DSRA Target references this independent row</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Formula: Scheduled DS = MAX(0, Debt - (Yr-1) x Sched Prin) x Rate + Sched Prin</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="32" t="inlineStr">
+        <is>
+          <t>--- ALTERNATIVE SCENARIOS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>ALTERNATIVE SCENARIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>A. Sculpted Debt (not sweep):</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Principal = CFADS / Target DSCR - Interest</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - No sweep mechanics needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>B. Contracted Revenue (PPA/Hedge):</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Use contract price, not merchant</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - More debt capacity</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>C. Major Maintenance Reserve:</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Add MRA similar to DSRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Funds hot gas path inspection</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="32" t="inlineStr">
+        <is>
+          <t>--- QA CHECKS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>QA CHECKS TO VERIFY MODEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>1. S&amp;U Balance: =IF(ABS(Uses-Sources)&lt;0.01,"PASS","FAIL")</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2. Debt Payoff: Ending Bal near $0 by tenor end</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>3. Min DSCR: Use MINIFS to exclude post-payoff zeros</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>4. DSRA: Never negative; releases at debt payoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>5. Sign Convention: Outflows negative, inflows positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>6. No Circular Refs: Excel shouldn't show warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="32" t="inlineStr">
+        <is>
+          <t>--- HINTS &amp; PITFALLS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="35" t="inlineStr">
+        <is>
+          <t>* Spark spread: $1/MWh x 1.76M MWh = $1.76mm EBITDA impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="35" t="inlineStr">
+        <is>
+          <t>* CF is NET of outages - don't double-count FOR in generation</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="35" t="inlineStr">
+        <is>
+          <t>* FOR only derates UCAP for capacity revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="35" t="inlineStr">
+        <is>
+          <t>* Fuel divisor is 1E9 (billion), not 1E6 (million)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="32" t="inlineStr">
+        <is>
+          <t>--- INTERVIEW QUESTIONS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Q: Walk me through how $5/MWh power price change affects IRR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Q: Why cash sweep instead of sculpted debt?</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Q: What would make you walk away from this deal?</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Q: How would you hedge the spark spread exposure?</t>
         </is>
       </c>
     </row>
@@ -1498,38 +2148,60 @@
           <t>CCGT Model - Lotus Infrastructure Partners</t>
         </is>
       </c>
-      <c r="D1" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G1" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H1" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I1" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J1" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K1" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="L1" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M1" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="N1" s="2" t="n">
-        <v>10</v>
+      <c r="D1" s="33" t="inlineStr">
+        <is>
+          <t>Y0 (2025)</t>
+        </is>
+      </c>
+      <c r="E1" s="33" t="inlineStr">
+        <is>
+          <t>Y1 (2026)</t>
+        </is>
+      </c>
+      <c r="F1" s="33" t="inlineStr">
+        <is>
+          <t>Y2 (2027)</t>
+        </is>
+      </c>
+      <c r="G1" s="33" t="inlineStr">
+        <is>
+          <t>Y3 (2028)</t>
+        </is>
+      </c>
+      <c r="H1" s="33" t="inlineStr">
+        <is>
+          <t>Y4 (2029)</t>
+        </is>
+      </c>
+      <c r="I1" s="33" t="inlineStr">
+        <is>
+          <t>Y5 (2030)</t>
+        </is>
+      </c>
+      <c r="J1" s="33" t="inlineStr">
+        <is>
+          <t>Y6 (2031)</t>
+        </is>
+      </c>
+      <c r="K1" s="33" t="inlineStr">
+        <is>
+          <t>Y7 (2032)</t>
+        </is>
+      </c>
+      <c r="L1" s="33" t="inlineStr">
+        <is>
+          <t>Y8 (2033)</t>
+        </is>
+      </c>
+      <c r="M1" s="33" t="inlineStr">
+        <is>
+          <t>Y9 (2034)</t>
+        </is>
+      </c>
+      <c r="N1" s="33" t="inlineStr">
+        <is>
+          <t>Y10 (2035)</t>
+        </is>
       </c>
     </row>
     <row r="2">

--- a/deliverables/deliverables-20260120-0030/Model_1_CCGT.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_1_CCGT.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -111,6 +111,14 @@
       <i val="1"/>
       <color rgb="00666666"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -162,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -236,6 +244,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3589,7 +3599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N151"/>
+  <dimension ref="A1:N147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3710,6 +3720,11 @@
         <f>$D$17</f>
         <v/>
       </c>
+      <c r="M3" s="53" t="inlineStr">
+        <is>
+          <t>IRR Sensitivity:</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -3730,6 +3745,11 @@
       <c r="D4" s="7">
         <f>E74</f>
         <v/>
+      </c>
+      <c r="M4" s="54" t="inlineStr">
+        <is>
+          <t>+/- 5% Entry → ~+/- 1% IRR</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -3741,6 +3761,11 @@
       <c r="B5" s="45" t="n"/>
       <c r="C5" s="45" t="n"/>
       <c r="D5" s="45" t="n"/>
+      <c r="M5" s="54" t="inlineStr">
+        <is>
+          <t>+/- 0.5x Exit → ~+/- 1.5% IRR</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="45" t="n"/>
@@ -5145,17 +5170,7 @@
           <t>[WHAT] Spark Spread = Power Price - (Plant HR × Gas / 1000)
 [WHY] Gross margin per MWh after fuel. Core driver of thermal profitability.
 [RMHR EQUIVALENCE - For Interview Discussion]
-Traders express this as "Market Heat Rate":
-  RMHR = Power / Gas × 1000
-  If RMHR &gt; Plant HR → "In the money" → Dispatch
-Spark Spread = (RMHR - Plant HR) × Gas / 1000
-Same math, different framing. Use Spark Spread in model (simpler).
-[EXAMPLE] Power=$50, Gas=$5, HR=7000
-  RMHR = 50/5 × 1000 = 10,000 Btu/kWh
-  Spread = 10,000 - 7,000 = 3,000 Btu/kWh
-  Spark = 3,000 × $5 / 1000 = $15/MWh ✓
-  (Or directly: $50 - 7×$5 = $15/MWh)
-[UNITS] $/MWh - (Btu/kWh × $/MMBtu / 1000) = $/MWh ✓</t>
+Traders express this as "Market Heat Rate":</t>
         </is>
       </c>
       <c r="E81" s="52">
@@ -7150,10 +7165,6 @@
         <v/>
       </c>
     </row>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="D7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -7177,7 +7188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N151"/>
+  <dimension ref="A1:N147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -7584,8 +7595,6 @@
         <v/>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
@@ -7686,7 +7695,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
@@ -7787,7 +7795,6 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="38"/>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
@@ -7888,7 +7895,6 @@
         <v>0.025</v>
       </c>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
@@ -7949,7 +7955,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48"/>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
@@ -8090,7 +8095,6 @@
         <v>1.1</v>
       </c>
     </row>
-    <row r="56"/>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
@@ -8171,8 +8175,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="61"/>
-    <row r="62"/>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
@@ -8298,8 +8300,6 @@
         <v/>
       </c>
     </row>
-    <row r="69"/>
-    <row r="70"/>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
@@ -8491,7 +8491,6 @@
         <v/>
       </c>
     </row>
-    <row r="75"/>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
@@ -8659,7 +8658,6 @@
         <v/>
       </c>
     </row>
-    <row r="79"/>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
@@ -8954,7 +8952,6 @@
         <v/>
       </c>
     </row>
-    <row r="85"/>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
@@ -9012,8 +9009,6 @@
         <v/>
       </c>
     </row>
-    <row r="87"/>
-    <row r="88"/>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
@@ -9205,8 +9200,6 @@
         <v/>
       </c>
     </row>
-    <row r="93"/>
-    <row r="94"/>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
@@ -9797,7 +9790,6 @@
         <v/>
       </c>
     </row>
-    <row r="106"/>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
@@ -10058,8 +10050,6 @@
         <v/>
       </c>
     </row>
-    <row r="112"/>
-    <row r="113"/>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
@@ -10247,8 +10237,6 @@
         <v/>
       </c>
     </row>
-    <row r="118"/>
-    <row r="119"/>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
@@ -10346,7 +10334,6 @@
         <v/>
       </c>
     </row>
-    <row r="126"/>
     <row r="127">
       <c r="A127" s="23" t="inlineStr">
         <is>
@@ -10424,8 +10411,6 @@
         <v/>
       </c>
     </row>
-    <row r="132"/>
-    <row r="133"/>
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
@@ -10530,7 +10515,6 @@
         <v/>
       </c>
     </row>
-    <row r="139"/>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
@@ -10650,7 +10634,6 @@
         <v/>
       </c>
     </row>
-    <row r="144"/>
     <row r="145">
       <c r="A145" s="23" t="inlineStr">
         <is>
@@ -10738,10 +10721,6 @@
         <v/>
       </c>
     </row>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/deliverables/deliverables-20260120-0030/Model_1_CCGT.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_1_CCGT.xlsx
@@ -170,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -246,6 +246,7 @@
     <xf numFmtId="4" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3599,7 +3600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N147"/>
+  <dimension ref="A1:N148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3717,7 +3718,7 @@
         </is>
       </c>
       <c r="D3" s="7">
-        <f>$D$17</f>
+        <f>$D$28</f>
         <v/>
       </c>
       <c r="M3" s="53" t="inlineStr">
@@ -3743,7 +3744,7 @@
         </is>
       </c>
       <c r="D4" s="7">
-        <f>E74</f>
+        <f>E86</f>
         <v/>
       </c>
       <c r="M4" s="54" t="inlineStr">
@@ -3987,7 +3988,7 @@
       <c r="B22" s="6" t="inlineStr"/>
       <c r="C22" s="6" t="inlineStr"/>
       <c r="D22" s="10">
-        <f>D119</f>
+        <f>D132</f>
         <v/>
       </c>
     </row>
@@ -4000,7 +4001,7 @@
       <c r="B23" s="6" t="inlineStr"/>
       <c r="C23" s="6" t="inlineStr"/>
       <c r="D23" s="10">
-        <f>IF(K91&lt;1,"PASS","FAIL")</f>
+        <f>IF(K103&lt;1,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
@@ -4017,12 +4018,10 @@
         </is>
       </c>
       <c r="D24" s="10">
-        <f>IF(D6&gt;=1.25,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26"/>
+        <f>IF(MIN(E104:K104)&gt;=1.25,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
@@ -4123,7 +4122,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
@@ -4224,7 +4222,6 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="38"/>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
@@ -4325,7 +4322,6 @@
         <v>0.025</v>
       </c>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
@@ -4386,7 +4382,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48"/>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
@@ -4527,7 +4522,6 @@
         <v>1.1</v>
       </c>
     </row>
-    <row r="56"/>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
@@ -4608,8 +4602,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="61"/>
-    <row r="62"/>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
@@ -4647,7 +4639,7 @@
         </is>
       </c>
       <c r="D64" s="16">
-        <f>$D$23*(1-$D$26)</f>
+        <f>$D$34*(1-$D$37)</f>
         <v/>
       </c>
     </row>
@@ -4668,7 +4660,7 @@
         </is>
       </c>
       <c r="D65" s="17">
-        <f>$D$23*$D$25*8760</f>
+        <f>$D$34*$D$36*8760*(1-$D$37)</f>
         <v/>
       </c>
     </row>
@@ -4689,7 +4681,7 @@
         </is>
       </c>
       <c r="D66" s="18">
-        <f>$D$17*$D$39</f>
+        <f>$D$28*$D$50</f>
         <v/>
       </c>
     </row>
@@ -4710,7 +4702,7 @@
         </is>
       </c>
       <c r="D67" s="18">
-        <f>$D$17*$D$48/$D$49</f>
+        <f>$D$28*$D$59/$D$60</f>
         <v/>
       </c>
     </row>
@@ -4731,12 +4723,10 @@
         </is>
       </c>
       <c r="D68" s="18">
-        <f>$D$55/$D$41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69"/>
-    <row r="70"/>
+        <f>$D$66/$D$52</f>
+        <v/>
+      </c>
+    </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
@@ -4774,43 +4764,43 @@
         </is>
       </c>
       <c r="E72" s="18">
-        <f>$D$29*(1+$D$32)^(1-1)</f>
+        <f>$D$40*(1+$D$43)^(1-1)</f>
         <v/>
       </c>
       <c r="F72" s="18">
-        <f>$D$29*(1+$D$32)^(2-1)</f>
+        <f>$D$40*(1+$D$43)^(2-1)</f>
         <v/>
       </c>
       <c r="G72" s="18">
-        <f>$D$29*(1+$D$32)^(3-1)</f>
+        <f>$D$40*(1+$D$43)^(3-1)</f>
         <v/>
       </c>
       <c r="H72" s="18">
-        <f>$D$29*(1+$D$32)^(4-1)</f>
+        <f>$D$40*(1+$D$43)^(4-1)</f>
         <v/>
       </c>
       <c r="I72" s="18">
-        <f>$D$29*(1+$D$32)^(5-1)</f>
+        <f>$D$40*(1+$D$43)^(5-1)</f>
         <v/>
       </c>
       <c r="J72" s="18">
-        <f>$D$29*(1+$D$32)^(6-1)</f>
+        <f>$D$40*(1+$D$43)^(6-1)</f>
         <v/>
       </c>
       <c r="K72" s="18">
-        <f>$D$29*(1+$D$32)^(7-1)</f>
+        <f>$D$40*(1+$D$43)^(7-1)</f>
         <v/>
       </c>
       <c r="L72" s="18">
-        <f>$D$29*(1+$D$32)^(8-1)</f>
+        <f>$D$40*(1+$D$43)^(8-1)</f>
         <v/>
       </c>
       <c r="M72" s="18">
-        <f>$D$29*(1+$D$32)^(9-1)</f>
+        <f>$D$40*(1+$D$43)^(9-1)</f>
         <v/>
       </c>
       <c r="N72" s="18">
-        <f>$D$29*(1+$D$32)^(10-1)</f>
+        <f>$D$40*(1+$D$43)^(10-1)</f>
         <v/>
       </c>
     </row>
@@ -4831,43 +4821,43 @@
         </is>
       </c>
       <c r="E73" s="18">
-        <f>$D$30*(1+$D$32)^(1-1)</f>
+        <f>$D$41*(1+$D$43)^(1-1)</f>
         <v/>
       </c>
       <c r="F73" s="18">
-        <f>$D$30*(1+$D$32)^(2-1)</f>
+        <f>$D$41*(1+$D$43)^(2-1)</f>
         <v/>
       </c>
       <c r="G73" s="18">
-        <f>$D$30*(1+$D$32)^(3-1)</f>
+        <f>$D$41*(1+$D$43)^(3-1)</f>
         <v/>
       </c>
       <c r="H73" s="18">
-        <f>$D$30*(1+$D$32)^(4-1)</f>
+        <f>$D$41*(1+$D$43)^(4-1)</f>
         <v/>
       </c>
       <c r="I73" s="18">
-        <f>$D$30*(1+$D$32)^(5-1)</f>
+        <f>$D$41*(1+$D$43)^(5-1)</f>
         <v/>
       </c>
       <c r="J73" s="18">
-        <f>$D$30*(1+$D$32)^(6-1)</f>
+        <f>$D$41*(1+$D$43)^(6-1)</f>
         <v/>
       </c>
       <c r="K73" s="18">
-        <f>$D$30*(1+$D$32)^(7-1)</f>
+        <f>$D$41*(1+$D$43)^(7-1)</f>
         <v/>
       </c>
       <c r="L73" s="18">
-        <f>$D$30*(1+$D$32)^(8-1)</f>
+        <f>$D$41*(1+$D$43)^(8-1)</f>
         <v/>
       </c>
       <c r="M73" s="18">
-        <f>$D$30*(1+$D$32)^(9-1)</f>
+        <f>$D$41*(1+$D$43)^(9-1)</f>
         <v/>
       </c>
       <c r="N73" s="18">
-        <f>$D$30*(1+$D$32)^(10-1)</f>
+        <f>$D$41*(1+$D$43)^(10-1)</f>
         <v/>
       </c>
     </row>
@@ -4888,47 +4878,46 @@
         </is>
       </c>
       <c r="E74" s="19">
-        <f>$D$31*(1+$D$32)^(1-1)</f>
+        <f>$D$42*(1+$D$43)^(1-1)</f>
         <v/>
       </c>
       <c r="F74" s="19">
-        <f>$D$31*(1+$D$32)^(2-1)</f>
+        <f>$D$42*(1+$D$43)^(2-1)</f>
         <v/>
       </c>
       <c r="G74" s="19">
-        <f>$D$31*(1+$D$32)^(3-1)</f>
+        <f>$D$42*(1+$D$43)^(3-1)</f>
         <v/>
       </c>
       <c r="H74" s="19">
-        <f>$D$31*(1+$D$32)^(4-1)</f>
+        <f>$D$42*(1+$D$43)^(4-1)</f>
         <v/>
       </c>
       <c r="I74" s="19">
-        <f>$D$31*(1+$D$32)^(5-1)</f>
+        <f>$D$42*(1+$D$43)^(5-1)</f>
         <v/>
       </c>
       <c r="J74" s="19">
-        <f>$D$31*(1+$D$32)^(6-1)</f>
+        <f>$D$42*(1+$D$43)^(6-1)</f>
         <v/>
       </c>
       <c r="K74" s="19">
-        <f>$D$31*(1+$D$32)^(7-1)</f>
+        <f>$D$42*(1+$D$43)^(7-1)</f>
         <v/>
       </c>
       <c r="L74" s="19">
-        <f>$D$31*(1+$D$32)^(8-1)</f>
+        <f>$D$42*(1+$D$43)^(8-1)</f>
         <v/>
       </c>
       <c r="M74" s="19">
-        <f>$D$31*(1+$D$32)^(9-1)</f>
+        <f>$D$42*(1+$D$43)^(9-1)</f>
         <v/>
       </c>
       <c r="N74" s="19">
-        <f>$D$31*(1+$D$32)^(10-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75"/>
+        <f>$D$42*(1+$D$43)^(10-1)</f>
+        <v/>
+      </c>
+    </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
@@ -4946,43 +4935,43 @@
         </is>
       </c>
       <c r="E76" s="18">
-        <f>$D$54*E61/1000000</f>
+        <f>$D$65*E72/1000000</f>
         <v/>
       </c>
       <c r="F76" s="18">
-        <f>$D$54*F61/1000000</f>
+        <f>$D$65*F72/1000000</f>
         <v/>
       </c>
       <c r="G76" s="18">
-        <f>$D$54*G61/1000000</f>
+        <f>$D$65*G72/1000000</f>
         <v/>
       </c>
       <c r="H76" s="18">
-        <f>$D$54*H61/1000000</f>
+        <f>$D$65*H72/1000000</f>
         <v/>
       </c>
       <c r="I76" s="18">
-        <f>$D$54*I61/1000000</f>
+        <f>$D$65*I72/1000000</f>
         <v/>
       </c>
       <c r="J76" s="18">
-        <f>$D$54*J61/1000000</f>
+        <f>$D$65*J72/1000000</f>
         <v/>
       </c>
       <c r="K76" s="18">
-        <f>$D$54*K61/1000000</f>
+        <f>$D$65*K72/1000000</f>
         <v/>
       </c>
       <c r="L76" s="18">
-        <f>$D$54*L61/1000000</f>
+        <f>$D$65*L72/1000000</f>
         <v/>
       </c>
       <c r="M76" s="18">
-        <f>$D$54*M61/1000000</f>
+        <f>$D$65*M72/1000000</f>
         <v/>
       </c>
       <c r="N76" s="18">
-        <f>$D$54*N61/1000000</f>
+        <f>$D$65*N72/1000000</f>
         <v/>
       </c>
     </row>
@@ -5003,43 +4992,43 @@
         </is>
       </c>
       <c r="E77" s="18">
-        <f>$D$53*E62*1000/1000000</f>
+        <f>$D$34*E73*1000/1000000</f>
         <v/>
       </c>
       <c r="F77" s="18">
-        <f>$D$53*F62*1000/1000000</f>
+        <f>$D$34*F73*1000/1000000</f>
         <v/>
       </c>
       <c r="G77" s="18">
-        <f>$D$53*G62*1000/1000000</f>
+        <f>$D$34*G73*1000/1000000</f>
         <v/>
       </c>
       <c r="H77" s="18">
-        <f>$D$53*H62*1000/1000000</f>
+        <f>$D$34*H73*1000/1000000</f>
         <v/>
       </c>
       <c r="I77" s="18">
-        <f>$D$53*I62*1000/1000000</f>
+        <f>$D$34*I73*1000/1000000</f>
         <v/>
       </c>
       <c r="J77" s="18">
-        <f>$D$53*J62*1000/1000000</f>
+        <f>$D$34*J73*1000/1000000</f>
         <v/>
       </c>
       <c r="K77" s="18">
-        <f>$D$53*K62*1000/1000000</f>
+        <f>$D$34*K73*1000/1000000</f>
         <v/>
       </c>
       <c r="L77" s="18">
-        <f>$D$53*L62*1000/1000000</f>
+        <f>$D$34*L73*1000/1000000</f>
         <v/>
       </c>
       <c r="M77" s="18">
-        <f>$D$53*M62*1000/1000000</f>
+        <f>$D$34*M73*1000/1000000</f>
         <v/>
       </c>
       <c r="N77" s="18">
-        <f>$D$53*N62*1000/1000000</f>
+        <f>$D$34*N73*1000/1000000</f>
         <v/>
       </c>
     </row>
@@ -5056,47 +5045,46 @@
       </c>
       <c r="C78" s="6" t="inlineStr"/>
       <c r="E78" s="20">
-        <f>E65+E66</f>
+        <f>E76+E77</f>
         <v/>
       </c>
       <c r="F78" s="20">
-        <f>F65+F66</f>
+        <f>F76+F77</f>
         <v/>
       </c>
       <c r="G78" s="20">
-        <f>G65+G66</f>
+        <f>G76+G77</f>
         <v/>
       </c>
       <c r="H78" s="20">
-        <f>H65+H66</f>
+        <f>H76+H77</f>
         <v/>
       </c>
       <c r="I78" s="20">
-        <f>I65+I66</f>
+        <f>I76+I77</f>
         <v/>
       </c>
       <c r="J78" s="20">
-        <f>J65+J66</f>
+        <f>J76+J77</f>
         <v/>
       </c>
       <c r="K78" s="20">
-        <f>K65+K66</f>
+        <f>K76+K77</f>
         <v/>
       </c>
       <c r="L78" s="20">
-        <f>L65+L66</f>
+        <f>L76+L77</f>
         <v/>
       </c>
       <c r="M78" s="20">
-        <f>M65+M66</f>
+        <f>M76+M77</f>
         <v/>
       </c>
       <c r="N78" s="20">
-        <f>N65+N66</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79"/>
+        <f>N76+N77</f>
+        <v/>
+      </c>
+    </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
@@ -5114,43 +5102,43 @@
         </is>
       </c>
       <c r="E80" s="18">
-        <f>$D$54*$D$24*E63/1E9</f>
+        <f>$D$65*$D$35*E74/1000000000</f>
         <v/>
       </c>
       <c r="F80" s="18">
-        <f>$D$54*$D$24*F63/1E9</f>
+        <f>$D$65*$D$35*F74/1000000000</f>
         <v/>
       </c>
       <c r="G80" s="18">
-        <f>$D$54*$D$24*G63/1E9</f>
+        <f>$D$65*$D$35*G74/1000000000</f>
         <v/>
       </c>
       <c r="H80" s="18">
-        <f>$D$54*$D$24*H63/1E9</f>
+        <f>$D$65*$D$35*H74/1000000000</f>
         <v/>
       </c>
       <c r="I80" s="18">
-        <f>$D$54*$D$24*I63/1E9</f>
+        <f>$D$65*$D$35*I74/1000000000</f>
         <v/>
       </c>
       <c r="J80" s="18">
-        <f>$D$54*$D$24*J63/1E9</f>
+        <f>$D$65*$D$35*J74/1000000000</f>
         <v/>
       </c>
       <c r="K80" s="18">
-        <f>$D$54*$D$24*K63/1E9</f>
+        <f>$D$65*$D$35*K74/1000000000</f>
         <v/>
       </c>
       <c r="L80" s="18">
-        <f>$D$54*$D$24*L63/1E9</f>
+        <f>$D$65*$D$35*L74/1000000000</f>
         <v/>
       </c>
       <c r="M80" s="18">
-        <f>$D$54*$D$24*M63/1E9</f>
+        <f>$D$65*$D$35*M74/1000000000</f>
         <v/>
       </c>
       <c r="N80" s="18">
-        <f>$D$54*$D$24*N63/1E9</f>
+        <f>$D$65*$D$35*N74/1000000000</f>
         <v/>
       </c>
     </row>
@@ -5174,43 +5162,43 @@
         </is>
       </c>
       <c r="E81" s="52">
-        <f>E71-($D$34/1000)*E73</f>
+        <f>E72-($D$35/1000)*E74</f>
         <v/>
       </c>
       <c r="F81" s="52">
-        <f>F71-($D$34/1000)*F73</f>
+        <f>F72-($D$35/1000)*F74</f>
         <v/>
       </c>
       <c r="G81" s="52">
-        <f>G71-($D$34/1000)*G73</f>
+        <f>G72-($D$35/1000)*G74</f>
         <v/>
       </c>
       <c r="H81" s="52">
-        <f>H71-($D$34/1000)*H73</f>
+        <f>H72-($D$35/1000)*H74</f>
         <v/>
       </c>
       <c r="I81" s="52">
-        <f>I71-($D$34/1000)*I73</f>
+        <f>I72-($D$35/1000)*I74</f>
         <v/>
       </c>
       <c r="J81" s="52">
-        <f>J71-($D$34/1000)*J73</f>
+        <f>J72-($D$35/1000)*J74</f>
         <v/>
       </c>
       <c r="K81" s="52">
-        <f>K71-($D$34/1000)*K73</f>
+        <f>K72-($D$35/1000)*K74</f>
         <v/>
       </c>
       <c r="L81" s="52">
-        <f>L71-($D$34/1000)*L73</f>
+        <f>L72-($D$35/1000)*L74</f>
         <v/>
       </c>
       <c r="M81" s="52">
-        <f>M71-($D$34/1000)*M73</f>
+        <f>M72-($D$35/1000)*M74</f>
         <v/>
       </c>
       <c r="N81" s="52">
-        <f>N71-($D$34/1000)*N73</f>
+        <f>N72-($D$35/1000)*N74</f>
         <v/>
       </c>
     </row>
@@ -5231,43 +5219,43 @@
         </is>
       </c>
       <c r="E82" s="18">
-        <f>$D$54*$D$35/1000000</f>
+        <f>$D$65*$D$46/1000000</f>
         <v/>
       </c>
       <c r="F82" s="18">
-        <f>$D$54*$D$35/1000000</f>
+        <f>$D$65*$D$46/1000000</f>
         <v/>
       </c>
       <c r="G82" s="18">
-        <f>$D$54*$D$35/1000000</f>
+        <f>$D$65*$D$46/1000000</f>
         <v/>
       </c>
       <c r="H82" s="18">
-        <f>$D$54*$D$35/1000000</f>
+        <f>$D$65*$D$46/1000000</f>
         <v/>
       </c>
       <c r="I82" s="18">
-        <f>$D$54*$D$35/1000000</f>
+        <f>$D$65*$D$46/1000000</f>
         <v/>
       </c>
       <c r="J82" s="18">
-        <f>$D$54*$D$35/1000000</f>
+        <f>$D$65*$D$46/1000000</f>
         <v/>
       </c>
       <c r="K82" s="18">
-        <f>$D$54*$D$35/1000000</f>
+        <f>$D$65*$D$46/1000000</f>
         <v/>
       </c>
       <c r="L82" s="18">
-        <f>$D$54*$D$35/1000000</f>
+        <f>$D$65*$D$46/1000000</f>
         <v/>
       </c>
       <c r="M82" s="18">
-        <f>$D$54*$D$35/1000000</f>
+        <f>$D$65*$D$46/1000000</f>
         <v/>
       </c>
       <c r="N82" s="18">
-        <f>$D$54*$D$35/1000000</f>
+        <f>$D$65*$D$46/1000000</f>
         <v/>
       </c>
     </row>
@@ -5288,43 +5276,43 @@
         </is>
       </c>
       <c r="E83" s="18">
-        <f>$D$23*$D$36*(1+$D$32)^(1-1)*1000/1000000</f>
+        <f>$D$34*$D$47*1000/1000000</f>
         <v/>
       </c>
       <c r="F83" s="18">
-        <f>$D$23*$D$36*(1+$D$32)^(2-1)*1000/1000000</f>
+        <f>$D$34*$D$47*1000/1000000</f>
         <v/>
       </c>
       <c r="G83" s="18">
-        <f>$D$23*$D$36*(1+$D$32)^(3-1)*1000/1000000</f>
+        <f>$D$34*$D$47*1000/1000000</f>
         <v/>
       </c>
       <c r="H83" s="18">
-        <f>$D$23*$D$36*(1+$D$32)^(4-1)*1000/1000000</f>
+        <f>$D$34*$D$47*1000/1000000</f>
         <v/>
       </c>
       <c r="I83" s="18">
-        <f>$D$23*$D$36*(1+$D$32)^(5-1)*1000/1000000</f>
+        <f>$D$34*$D$47*1000/1000000</f>
         <v/>
       </c>
       <c r="J83" s="18">
-        <f>$D$23*$D$36*(1+$D$32)^(6-1)*1000/1000000</f>
+        <f>$D$34*$D$47*1000/1000000</f>
         <v/>
       </c>
       <c r="K83" s="18">
-        <f>$D$23*$D$36*(1+$D$32)^(7-1)*1000/1000000</f>
+        <f>$D$34*$D$47*1000/1000000</f>
         <v/>
       </c>
       <c r="L83" s="18">
-        <f>$D$23*$D$36*(1+$D$32)^(8-1)*1000/1000000</f>
+        <f>$D$34*$D$47*1000/1000000</f>
         <v/>
       </c>
       <c r="M83" s="18">
-        <f>$D$23*$D$36*(1+$D$32)^(9-1)*1000/1000000</f>
+        <f>$D$34*$D$47*1000/1000000</f>
         <v/>
       </c>
       <c r="N83" s="18">
-        <f>$D$23*$D$36*(1+$D$32)^(10-1)*1000/1000000</f>
+        <f>$D$34*$D$47*1000/1000000</f>
         <v/>
       </c>
     </row>
@@ -5341,47 +5329,46 @@
       </c>
       <c r="C84" s="6" t="inlineStr"/>
       <c r="E84" s="18">
-        <f>E69+E70+E71</f>
+        <f>E80+E82+E83</f>
         <v/>
       </c>
       <c r="F84" s="18">
-        <f>F69+F70+F71</f>
+        <f>F80+F82+F83</f>
         <v/>
       </c>
       <c r="G84" s="18">
-        <f>G69+G70+G71</f>
+        <f>G80+G82+G83</f>
         <v/>
       </c>
       <c r="H84" s="18">
-        <f>H69+H70+H71</f>
+        <f>H80+H82+H83</f>
         <v/>
       </c>
       <c r="I84" s="18">
-        <f>I69+I70+I71</f>
+        <f>I80+I82+I83</f>
         <v/>
       </c>
       <c r="J84" s="18">
-        <f>J69+J70+J71</f>
+        <f>J80+J82+J83</f>
         <v/>
       </c>
       <c r="K84" s="18">
-        <f>K69+K70+K71</f>
+        <f>K80+K82+K83</f>
         <v/>
       </c>
       <c r="L84" s="18">
-        <f>L69+L70+L71</f>
+        <f>L80+L82+L83</f>
         <v/>
       </c>
       <c r="M84" s="18">
-        <f>M69+M70+M71</f>
+        <f>M80+M82+M83</f>
         <v/>
       </c>
       <c r="N84" s="18">
-        <f>N69+N70+N71</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85"/>
+        <f>N80+N82+N83</f>
+        <v/>
+      </c>
+    </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
@@ -5399,48 +5386,46 @@
         </is>
       </c>
       <c r="E86" s="7">
-        <f>E67-E72</f>
+        <f>E78-E84</f>
         <v/>
       </c>
       <c r="F86" s="7">
-        <f>F67-F72</f>
+        <f>F78-F84</f>
         <v/>
       </c>
       <c r="G86" s="7">
-        <f>G67-G72</f>
+        <f>G78-G84</f>
         <v/>
       </c>
       <c r="H86" s="7">
-        <f>H67-H72</f>
+        <f>H78-H84</f>
         <v/>
       </c>
       <c r="I86" s="7">
-        <f>I67-I72</f>
+        <f>I78-I84</f>
         <v/>
       </c>
       <c r="J86" s="7">
-        <f>J67-J72</f>
+        <f>J78-J84</f>
         <v/>
       </c>
       <c r="K86" s="7">
-        <f>K67-K72</f>
+        <f>K78-K84</f>
         <v/>
       </c>
       <c r="L86" s="7">
-        <f>L67-L72</f>
+        <f>L78-L84</f>
         <v/>
       </c>
       <c r="M86" s="7">
-        <f>M67-M72</f>
+        <f>M78-M84</f>
         <v/>
       </c>
       <c r="N86" s="7">
-        <f>N67-N72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87"/>
-    <row r="88"/>
+        <f>N78-N84</f>
+        <v/>
+      </c>
+    </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
@@ -5478,43 +5463,43 @@
         </is>
       </c>
       <c r="E90" s="18">
-        <f>E74-$D$56</f>
+        <f>E86-$D$67</f>
         <v/>
       </c>
       <c r="F90" s="18">
-        <f>F74-$D$56</f>
+        <f>F86-$D$67</f>
         <v/>
       </c>
       <c r="G90" s="18">
-        <f>G74-$D$56</f>
+        <f>G86-$D$67</f>
         <v/>
       </c>
       <c r="H90" s="18">
-        <f>H74-$D$56</f>
+        <f>H86-$D$67</f>
         <v/>
       </c>
       <c r="I90" s="18">
-        <f>I74-$D$56</f>
+        <f>I86-$D$67</f>
         <v/>
       </c>
       <c r="J90" s="18">
-        <f>J74-$D$56</f>
+        <f>J86-$D$67</f>
         <v/>
       </c>
       <c r="K90" s="18">
-        <f>K74-$D$56</f>
+        <f>K86-$D$67</f>
         <v/>
       </c>
       <c r="L90" s="18">
-        <f>L74-$D$56</f>
+        <f>L86-$D$67</f>
         <v/>
       </c>
       <c r="M90" s="18">
-        <f>M74-$D$56</f>
+        <f>M86-$D$67</f>
         <v/>
       </c>
       <c r="N90" s="18">
-        <f>N74-$D$56</f>
+        <f>N86-$D$67</f>
         <v/>
       </c>
     </row>
@@ -5535,43 +5520,43 @@
         </is>
       </c>
       <c r="E91" s="18">
-        <f>MAX(0,E78)*$D$47</f>
+        <f>MAX(0,E90)*$D$58</f>
         <v/>
       </c>
       <c r="F91" s="18">
-        <f>MAX(0,F78)*$D$47</f>
+        <f>MAX(0,F90)*$D$58</f>
         <v/>
       </c>
       <c r="G91" s="18">
-        <f>MAX(0,G78)*$D$47</f>
+        <f>MAX(0,G90)*$D$58</f>
         <v/>
       </c>
       <c r="H91" s="18">
-        <f>MAX(0,H78)*$D$47</f>
+        <f>MAX(0,H90)*$D$58</f>
         <v/>
       </c>
       <c r="I91" s="18">
-        <f>MAX(0,I78)*$D$47</f>
+        <f>MAX(0,I90)*$D$58</f>
         <v/>
       </c>
       <c r="J91" s="18">
-        <f>MAX(0,J78)*$D$47</f>
+        <f>MAX(0,J90)*$D$58</f>
         <v/>
       </c>
       <c r="K91" s="18">
-        <f>MAX(0,K78)*$D$47</f>
+        <f>MAX(0,K90)*$D$58</f>
         <v/>
       </c>
       <c r="L91" s="18">
-        <f>MAX(0,L78)*$D$47</f>
+        <f>MAX(0,L90)*$D$58</f>
         <v/>
       </c>
       <c r="M91" s="18">
-        <f>MAX(0,M78)*$D$47</f>
+        <f>MAX(0,M90)*$D$58</f>
         <v/>
       </c>
       <c r="N91" s="18">
-        <f>MAX(0,N78)*$D$47</f>
+        <f>MAX(0,N90)*$D$58</f>
         <v/>
       </c>
     </row>
@@ -5592,48 +5577,46 @@
         </is>
       </c>
       <c r="E92" s="7">
-        <f>E74-E79</f>
+        <f>E86-E91</f>
         <v/>
       </c>
       <c r="F92" s="7">
-        <f>F74-F79</f>
+        <f>F86-F91</f>
         <v/>
       </c>
       <c r="G92" s="7">
-        <f>G74-G79</f>
+        <f>G86-G91</f>
         <v/>
       </c>
       <c r="H92" s="7">
-        <f>H74-H79</f>
+        <f>H86-H91</f>
         <v/>
       </c>
       <c r="I92" s="7">
-        <f>I74-I79</f>
+        <f>I86-I91</f>
         <v/>
       </c>
       <c r="J92" s="7">
-        <f>J74-J79</f>
+        <f>J86-J91</f>
         <v/>
       </c>
       <c r="K92" s="7">
-        <f>K74-K79</f>
+        <f>K86-K91</f>
         <v/>
       </c>
       <c r="L92" s="7">
-        <f>L74-L79</f>
+        <f>L86-L91</f>
         <v/>
       </c>
       <c r="M92" s="7">
-        <f>M74-M79</f>
+        <f>M86-M91</f>
         <v/>
       </c>
       <c r="N92" s="7">
-        <f>N74-N79</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93"/>
-    <row r="94"/>
+        <f>N86-N91</f>
+        <v/>
+      </c>
+    </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
@@ -5670,44 +5653,47 @@
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr"/>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
       <c r="E96" s="18">
-        <f>$D$55</f>
+        <f>$D$66</f>
         <v/>
       </c>
       <c r="F96" s="18">
-        <f>E91</f>
+        <f>E103</f>
         <v/>
       </c>
       <c r="G96" s="18">
-        <f>F91</f>
+        <f>F103</f>
         <v/>
       </c>
       <c r="H96" s="18">
-        <f>G91</f>
+        <f>G103</f>
         <v/>
       </c>
       <c r="I96" s="18">
-        <f>H91</f>
+        <f>H103</f>
         <v/>
       </c>
       <c r="J96" s="18">
-        <f>I91</f>
+        <f>I103</f>
         <v/>
       </c>
       <c r="K96" s="18">
-        <f>J91</f>
+        <f>J103</f>
         <v/>
       </c>
       <c r="L96" s="18">
-        <f>K91</f>
+        <f>K103</f>
         <v/>
       </c>
       <c r="M96" s="18">
-        <f>L91</f>
+        <f>L103</f>
         <v/>
       </c>
       <c r="N96" s="18">
-        <f>M91</f>
+        <f>M103</f>
         <v/>
       </c>
     </row>
@@ -5728,43 +5714,43 @@
         </is>
       </c>
       <c r="E97" s="18">
-        <f>E84*$D$40</f>
+        <f>E96*$D$51</f>
         <v/>
       </c>
       <c r="F97" s="18">
-        <f>F84*$D$40</f>
+        <f>F96*$D$51</f>
         <v/>
       </c>
       <c r="G97" s="18">
-        <f>G84*$D$40</f>
+        <f>G96*$D$51</f>
         <v/>
       </c>
       <c r="H97" s="18">
-        <f>H84*$D$40</f>
+        <f>H96*$D$51</f>
         <v/>
       </c>
       <c r="I97" s="18">
-        <f>I84*$D$40</f>
+        <f>I96*$D$51</f>
         <v/>
       </c>
       <c r="J97" s="18">
-        <f>J84*$D$40</f>
+        <f>J96*$D$51</f>
         <v/>
       </c>
       <c r="K97" s="18">
-        <f>K84*$D$40</f>
+        <f>K96*$D$51</f>
         <v/>
       </c>
       <c r="L97" s="18">
-        <f>L84*$D$40</f>
+        <f>L96*$D$51</f>
         <v/>
       </c>
       <c r="M97" s="18">
-        <f>M84*$D$40</f>
+        <f>M96*$D$51</f>
         <v/>
       </c>
       <c r="N97" s="18">
-        <f>N84*$D$40</f>
+        <f>N96*$D$51</f>
         <v/>
       </c>
     </row>
@@ -5785,43 +5771,43 @@
         </is>
       </c>
       <c r="E98" s="18">
-        <f>MIN($D$57,E84)</f>
+        <f>MIN($D$68,E96)</f>
         <v/>
       </c>
       <c r="F98" s="18">
-        <f>MIN($D$57,F84)</f>
+        <f>MIN($D$68,F96)</f>
         <v/>
       </c>
       <c r="G98" s="18">
-        <f>MIN($D$57,G84)</f>
+        <f>MIN($D$68,G96)</f>
         <v/>
       </c>
       <c r="H98" s="18">
-        <f>MIN($D$57,H84)</f>
+        <f>MIN($D$68,H96)</f>
         <v/>
       </c>
       <c r="I98" s="18">
-        <f>MIN($D$57,I84)</f>
+        <f>MIN($D$68,I96)</f>
         <v/>
       </c>
       <c r="J98" s="18">
-        <f>MIN($D$57,J84)</f>
+        <f>MIN($D$68,J96)</f>
         <v/>
       </c>
       <c r="K98" s="18">
-        <f>MIN($D$57,K84)</f>
+        <f>MIN($D$68,K96)</f>
         <v/>
       </c>
       <c r="L98" s="18">
-        <f>MIN($D$57,L84)</f>
+        <f>MIN($D$68,L96)</f>
         <v/>
       </c>
       <c r="M98" s="18">
-        <f>MIN($D$57,M84)</f>
+        <f>MIN($D$68,M96)</f>
         <v/>
       </c>
       <c r="N98" s="18">
-        <f>MIN($D$57,N84)</f>
+        <f>MIN($D$68,N96)</f>
         <v/>
       </c>
     </row>
@@ -5842,43 +5828,43 @@
         </is>
       </c>
       <c r="E99" s="18">
-        <f>E85+E86</f>
+        <f>E97+E98</f>
         <v/>
       </c>
       <c r="F99" s="18">
-        <f>F85+F86</f>
+        <f>F97+F98</f>
         <v/>
       </c>
       <c r="G99" s="18">
-        <f>G85+G86</f>
+        <f>G97+G98</f>
         <v/>
       </c>
       <c r="H99" s="18">
-        <f>H85+H86</f>
+        <f>H97+H98</f>
         <v/>
       </c>
       <c r="I99" s="18">
-        <f>I85+I86</f>
+        <f>I97+I98</f>
         <v/>
       </c>
       <c r="J99" s="18">
-        <f>J85+J86</f>
+        <f>J97+J98</f>
         <v/>
       </c>
       <c r="K99" s="18">
-        <f>K85+K86</f>
+        <f>K97+K98</f>
         <v/>
       </c>
       <c r="L99" s="18">
-        <f>L85+L86</f>
+        <f>L97+L98</f>
         <v/>
       </c>
       <c r="M99" s="18">
-        <f>M85+M86</f>
+        <f>M97+M98</f>
         <v/>
       </c>
       <c r="N99" s="18">
-        <f>N85+N86</f>
+        <f>N97+N98</f>
         <v/>
       </c>
     </row>
@@ -5899,43 +5885,43 @@
         </is>
       </c>
       <c r="E100" s="18">
-        <f>MAX(0,E80-E87-E98)</f>
+        <f>MAX(0,E92-E99-E110)</f>
         <v/>
       </c>
       <c r="F100" s="18">
-        <f>MAX(0,F80-F87-F98)</f>
+        <f>MAX(0,F92-F99-F110)</f>
         <v/>
       </c>
       <c r="G100" s="18">
-        <f>MAX(0,G80-G87-G98)</f>
+        <f>MAX(0,G92-G99-G110)</f>
         <v/>
       </c>
       <c r="H100" s="18">
-        <f>MAX(0,H80-H87-H98)</f>
+        <f>MAX(0,H92-H99-H110)</f>
         <v/>
       </c>
       <c r="I100" s="18">
-        <f>MAX(0,I80-I87-I98)</f>
+        <f>MAX(0,I92-I99-I110)</f>
         <v/>
       </c>
       <c r="J100" s="18">
-        <f>MAX(0,J80-J87-J98)</f>
+        <f>MAX(0,J92-J99-J110)</f>
         <v/>
       </c>
       <c r="K100" s="18">
-        <f>MAX(0,K80-K87-K98)</f>
+        <f>MAX(0,K92-K99-K110)</f>
         <v/>
       </c>
       <c r="L100" s="18">
-        <f>MAX(0,L80-L87-L98)</f>
+        <f>MAX(0,L92-L99-L110)</f>
         <v/>
       </c>
       <c r="M100" s="18">
-        <f>MAX(0,M80-M87-M98)</f>
+        <f>MAX(0,M92-M99-M110)</f>
         <v/>
       </c>
       <c r="N100" s="18">
-        <f>MAX(0,N80-N87-N98)</f>
+        <f>MAX(0,N92-N99-N110)</f>
         <v/>
       </c>
     </row>
@@ -5956,43 +5942,43 @@
         </is>
       </c>
       <c r="E101" s="21">
-        <f>MIN(MAX(0,E88)*$D$43,MAX(0,E84-E86))</f>
+        <f>MIN(E100*$D$54,MAX(0,E96-E98))</f>
         <v/>
       </c>
       <c r="F101" s="21">
-        <f>MIN(MAX(0,F88)*$D$43,MAX(0,F84-F86))</f>
+        <f>MIN(F100*$D$54,MAX(0,F96-F98))</f>
         <v/>
       </c>
       <c r="G101" s="21">
-        <f>MIN(MAX(0,G88)*$D$43,MAX(0,G84-G86))</f>
+        <f>MIN(G100*$D$54,MAX(0,G96-G98))</f>
         <v/>
       </c>
       <c r="H101" s="21">
-        <f>MIN(MAX(0,H88)*$D$43,MAX(0,H84-H86))</f>
+        <f>MIN(H100*$D$54,MAX(0,H96-H98))</f>
         <v/>
       </c>
       <c r="I101" s="21">
-        <f>MIN(MAX(0,I88)*$D$43,MAX(0,I84-I86))</f>
+        <f>MIN(I100*$D$54,MAX(0,I96-I98))</f>
         <v/>
       </c>
       <c r="J101" s="21">
-        <f>MIN(MAX(0,J88)*$D$43,MAX(0,J84-J86))</f>
+        <f>MIN(J100*$D$54,MAX(0,J96-J98))</f>
         <v/>
       </c>
       <c r="K101" s="21">
-        <f>MIN(MAX(0,K88)*$D$43,MAX(0,K84-K86))</f>
+        <f>MIN(K100*$D$54,MAX(0,K96-K98))</f>
         <v/>
       </c>
       <c r="L101" s="21">
-        <f>MIN(MAX(0,L88)*$D$43,MAX(0,L84-L86))</f>
+        <f>MIN(L100*$D$54,MAX(0,L96-L98))</f>
         <v/>
       </c>
       <c r="M101" s="21">
-        <f>MIN(MAX(0,M88)*$D$43,MAX(0,M84-M86))</f>
+        <f>MIN(M100*$D$54,MAX(0,M96-M98))</f>
         <v/>
       </c>
       <c r="N101" s="21">
-        <f>MIN(MAX(0,N88)*$D$43,MAX(0,N84-N86))</f>
+        <f>MIN(N100*$D$54,MAX(0,N96-N98))</f>
         <v/>
       </c>
     </row>
@@ -6013,43 +5999,43 @@
         </is>
       </c>
       <c r="E102" s="18">
-        <f>E86+E89</f>
+        <f>E98+E101</f>
         <v/>
       </c>
       <c r="F102" s="18">
-        <f>F86+F89</f>
+        <f>F98+F101</f>
         <v/>
       </c>
       <c r="G102" s="18">
-        <f>G86+G89</f>
+        <f>G98+G101</f>
         <v/>
       </c>
       <c r="H102" s="18">
-        <f>H86+H89</f>
+        <f>H98+H101</f>
         <v/>
       </c>
       <c r="I102" s="18">
-        <f>I86+I89</f>
+        <f>I98+I101</f>
         <v/>
       </c>
       <c r="J102" s="18">
-        <f>J86+J89</f>
+        <f>J98+J101</f>
         <v/>
       </c>
       <c r="K102" s="18">
-        <f>K86+K89</f>
+        <f>K98+K101</f>
         <v/>
       </c>
       <c r="L102" s="18">
-        <f>L86+L89</f>
+        <f>L98+L101</f>
         <v/>
       </c>
       <c r="M102" s="18">
-        <f>M86+M89</f>
+        <f>M98+M101</f>
         <v/>
       </c>
       <c r="N102" s="18">
-        <f>N86+N89</f>
+        <f>N98+N101</f>
         <v/>
       </c>
     </row>
@@ -6069,44 +6055,48 @@
           <t>MAX(0, Beg - Total Prin)</t>
         </is>
       </c>
+      <c r="D103">
+        <f>$D$66</f>
+        <v/>
+      </c>
       <c r="E103" s="18">
-        <f>MAX(0,E84-E90)</f>
+        <f>MAX(0,E96-E102)</f>
         <v/>
       </c>
       <c r="F103" s="18">
-        <f>MAX(0,F84-F90)</f>
+        <f>MAX(0,F96-F102)</f>
         <v/>
       </c>
       <c r="G103" s="18">
-        <f>MAX(0,G84-G90)</f>
+        <f>MAX(0,G96-G102)</f>
         <v/>
       </c>
       <c r="H103" s="18">
-        <f>MAX(0,H84-H90)</f>
+        <f>MAX(0,H96-H102)</f>
         <v/>
       </c>
       <c r="I103" s="18">
-        <f>MAX(0,I84-I90)</f>
+        <f>MAX(0,I96-I102)</f>
         <v/>
       </c>
       <c r="J103" s="18">
-        <f>MAX(0,J84-J90)</f>
+        <f>MAX(0,J96-J102)</f>
         <v/>
       </c>
       <c r="K103" s="18">
-        <f>MAX(0,K84-K90)</f>
+        <f>MAX(0,K96-K102)</f>
         <v/>
       </c>
       <c r="L103" s="18">
-        <f>MAX(0,L84-L90)</f>
+        <f>MAX(0,L96-L102)</f>
         <v/>
       </c>
       <c r="M103" s="18">
-        <f>MAX(0,M84-M90)</f>
+        <f>MAX(0,M96-M102)</f>
         <v/>
       </c>
       <c r="N103" s="18">
-        <f>MAX(0,N84-N90)</f>
+        <f>MAX(0,N96-N102)</f>
         <v/>
       </c>
     </row>
@@ -6127,43 +6117,43 @@
         </is>
       </c>
       <c r="E104" s="24">
-        <f>IF(E87&gt;0,E80/E87,0)</f>
+        <f>IF(E99&gt;0,E92/E99,0)</f>
         <v/>
       </c>
       <c r="F104" s="24">
-        <f>IF(F87&gt;0,F80/F87,0)</f>
+        <f>IF(F99&gt;0,F92/F99,0)</f>
         <v/>
       </c>
       <c r="G104" s="24">
-        <f>IF(G87&gt;0,G80/G87,0)</f>
+        <f>IF(G99&gt;0,G92/G99,0)</f>
         <v/>
       </c>
       <c r="H104" s="24">
-        <f>IF(H87&gt;0,H80/H87,0)</f>
+        <f>IF(H99&gt;0,H92/H99,0)</f>
         <v/>
       </c>
       <c r="I104" s="24">
-        <f>IF(I87&gt;0,I80/I87,0)</f>
+        <f>IF(I99&gt;0,I92/I99,0)</f>
         <v/>
       </c>
       <c r="J104" s="24">
-        <f>IF(J87&gt;0,J80/J87,0)</f>
+        <f>IF(J99&gt;0,J92/J99,0)</f>
         <v/>
       </c>
       <c r="K104" s="24">
-        <f>IF(K87&gt;0,K80/K87,0)</f>
+        <f>IF(K99&gt;0,K92/K99,0)</f>
         <v/>
       </c>
       <c r="L104" s="24">
-        <f>IF(L87&gt;0,L80/L87,0)</f>
+        <f>IF(L99&gt;0,L92/L99,0)</f>
         <v/>
       </c>
       <c r="M104" s="24">
-        <f>IF(M87&gt;0,M80/M87,0)</f>
+        <f>IF(M99&gt;0,M92/M99,0)</f>
         <v/>
       </c>
       <c r="N104" s="24">
-        <f>IF(N87&gt;0,N80/N87,0)</f>
+        <f>IF(N99&gt;0,N92/N99,0)</f>
         <v/>
       </c>
     </row>
@@ -6224,7 +6214,48 @@
         <v/>
       </c>
     </row>
-    <row r="106"/>
+    <row r="106">
+      <c r="E106">
+        <f>MAX(0,$D$66-(1-1)*$D$68)*$D$51+$D$68</f>
+        <v/>
+      </c>
+      <c r="F106">
+        <f>MAX(0,$D$66-(2-1)*$D$68)*$D$51+$D$68</f>
+        <v/>
+      </c>
+      <c r="G106">
+        <f>MAX(0,$D$66-(3-1)*$D$68)*$D$51+$D$68</f>
+        <v/>
+      </c>
+      <c r="H106">
+        <f>MAX(0,$D$66-(4-1)*$D$68)*$D$51+$D$68</f>
+        <v/>
+      </c>
+      <c r="I106">
+        <f>MAX(0,$D$66-(5-1)*$D$68)*$D$51+$D$68</f>
+        <v/>
+      </c>
+      <c r="J106">
+        <f>MAX(0,$D$66-(6-1)*$D$68)*$D$51+$D$68</f>
+        <v/>
+      </c>
+      <c r="K106">
+        <f>MAX(0,$D$66-(7-1)*$D$68)*$D$51+$D$68</f>
+        <v/>
+      </c>
+      <c r="L106">
+        <f>MAX(0,$D$66-(8-1)*$D$68)*$D$51+$D$68</f>
+        <v/>
+      </c>
+      <c r="M106">
+        <f>MAX(0,$D$66-(9-1)*$D$68)*$D$51+$D$68</f>
+        <v/>
+      </c>
+      <c r="N106">
+        <f>MAX(0,$D$66-(10-1)*$D$68)*$D$51+$D$68</f>
+        <v/>
+      </c>
+    </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
@@ -6266,44 +6297,43 @@
         <v/>
       </c>
       <c r="E108" s="18">
-        <f>F93*$D$42/12</f>
+        <f>F106*$D$53/12</f>
         <v/>
       </c>
       <c r="F108" s="18">
-        <f>G93*$D$42/12</f>
+        <f>G106*$D$53/12</f>
         <v/>
       </c>
       <c r="G108" s="18">
-        <f>H93*$D$42/12</f>
+        <f>H106*$D$53/12</f>
         <v/>
       </c>
       <c r="H108" s="18">
-        <f>I93*$D$42/12</f>
+        <f>I106*$D$53/12</f>
         <v/>
       </c>
       <c r="I108" s="18">
-        <f>J93*$D$42/12</f>
+        <f>J106*$D$53/12</f>
         <v/>
       </c>
       <c r="J108" s="18">
-        <f>K93*$D$42/12</f>
+        <f>K106*$D$53/12</f>
         <v/>
       </c>
       <c r="K108" s="18">
-        <f>L93*$D$42/12</f>
+        <f>L106*$D$53/12</f>
         <v/>
       </c>
       <c r="L108" s="18">
-        <f>M93*$D$42/12</f>
+        <f>M106*$D$53/12</f>
         <v/>
       </c>
       <c r="M108" s="18">
-        <f>N93*$D$42/12</f>
-        <v/>
-      </c>
-      <c r="N108" s="18">
-        <f>0</f>
-        <v/>
+        <f>N106*$D$53/12</f>
+        <v/>
+      </c>
+      <c r="N108" s="18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -6318,48 +6348,47 @@
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr"/>
-      <c r="D109" s="18">
-        <f>0</f>
-        <v/>
+      <c r="D109" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="E109" s="18">
-        <f>D99</f>
+        <f>D124</f>
         <v/>
       </c>
       <c r="F109" s="18">
-        <f>E99</f>
+        <f>E111</f>
         <v/>
       </c>
       <c r="G109" s="18">
-        <f>F99</f>
+        <f>F111</f>
         <v/>
       </c>
       <c r="H109" s="18">
-        <f>G99</f>
+        <f>G111</f>
         <v/>
       </c>
       <c r="I109" s="18">
-        <f>H99</f>
+        <f>H111</f>
         <v/>
       </c>
       <c r="J109" s="18">
-        <f>I99</f>
+        <f>I111</f>
         <v/>
       </c>
       <c r="K109" s="18">
-        <f>J99</f>
+        <f>J111</f>
         <v/>
       </c>
       <c r="L109" s="18">
-        <f>K99</f>
+        <f>K111</f>
         <v/>
       </c>
       <c r="M109" s="18">
-        <f>L99</f>
+        <f>L111</f>
         <v/>
       </c>
       <c r="N109" s="18">
-        <f>M99</f>
+        <f>M111</f>
         <v/>
       </c>
     </row>
@@ -6384,43 +6413,43 @@
         <v/>
       </c>
       <c r="E110" s="18">
-        <f>E96-E97</f>
+        <f>E108-E109</f>
         <v/>
       </c>
       <c r="F110" s="18">
-        <f>F96-F97</f>
+        <f>F108-F109</f>
         <v/>
       </c>
       <c r="G110" s="18">
-        <f>G96-G97</f>
+        <f>G108-G109</f>
         <v/>
       </c>
       <c r="H110" s="18">
-        <f>H96-H97</f>
+        <f>H108-H109</f>
         <v/>
       </c>
       <c r="I110" s="18">
-        <f>I96-I97</f>
+        <f>I108-I109</f>
         <v/>
       </c>
       <c r="J110" s="18">
-        <f>J96-J97</f>
+        <f>J108-J109</f>
         <v/>
       </c>
       <c r="K110" s="18">
-        <f>K96-K97</f>
+        <f>K108-K109</f>
         <v/>
       </c>
       <c r="L110" s="18">
-        <f>L96-L97</f>
+        <f>L108-L109</f>
         <v/>
       </c>
       <c r="M110" s="18">
-        <f>M96-M97</f>
+        <f>M108-M109</f>
         <v/>
       </c>
       <c r="N110" s="18">
-        <f>N96-N97</f>
+        <f>N108-N109</f>
         <v/>
       </c>
     </row>
@@ -6445,48 +6474,46 @@
         <v/>
       </c>
       <c r="E111" s="18">
-        <f>E97+E98</f>
+        <f>E109+E110</f>
         <v/>
       </c>
       <c r="F111" s="18">
-        <f>F97+F98</f>
+        <f>F109+F110</f>
         <v/>
       </c>
       <c r="G111" s="18">
-        <f>G97+G98</f>
+        <f>G109+G110</f>
         <v/>
       </c>
       <c r="H111" s="18">
-        <f>H97+H98</f>
+        <f>H109+H110</f>
         <v/>
       </c>
       <c r="I111" s="18">
-        <f>I97+I98</f>
+        <f>I109+I110</f>
         <v/>
       </c>
       <c r="J111" s="18">
-        <f>J97+J98</f>
+        <f>J109+J110</f>
         <v/>
       </c>
       <c r="K111" s="18">
-        <f>K97+K98</f>
+        <f>K109+K110</f>
         <v/>
       </c>
       <c r="L111" s="18">
-        <f>L97+L98</f>
+        <f>L109+L110</f>
         <v/>
       </c>
       <c r="M111" s="18">
-        <f>M97+M98</f>
+        <f>M109+M110</f>
         <v/>
       </c>
       <c r="N111" s="18">
-        <f>N97+N98</f>
-        <v/>
-      </c>
-    </row>
-    <row r="112"/>
-    <row r="113"/>
+        <f>N109+N110</f>
+        <v/>
+      </c>
+    </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
@@ -6524,43 +6551,43 @@
         </is>
       </c>
       <c r="E115" s="18">
-        <f>E80-(E85+E90)-E98</f>
+        <f>E92-E97-E102-E110</f>
         <v/>
       </c>
       <c r="F115" s="18">
-        <f>F80-(F85+F90)-F98</f>
+        <f>F92-F97-F102-F110</f>
         <v/>
       </c>
       <c r="G115" s="18">
-        <f>G80-(G85+G90)-G98</f>
+        <f>G92-G97-G102-G110</f>
         <v/>
       </c>
       <c r="H115" s="18">
-        <f>H80-(H85+H90)-H98</f>
+        <f>H92-H97-H102-H110</f>
         <v/>
       </c>
       <c r="I115" s="18">
-        <f>I80-(I85+I90)-I98</f>
+        <f>I92-I97-I102-I110</f>
         <v/>
       </c>
       <c r="J115" s="18">
-        <f>J80-(J85+J90)-J98</f>
+        <f>J92-J97-J102-J110</f>
         <v/>
       </c>
       <c r="K115" s="18">
-        <f>K80-(K85+K90)-K98</f>
+        <f>K92-K97-K102-K110</f>
         <v/>
       </c>
       <c r="L115" s="18">
-        <f>L80-(L85+L90)-L98</f>
+        <f>L92-L97-L102-L110</f>
         <v/>
       </c>
       <c r="M115" s="18">
-        <f>M80-(M85+M90)-M98</f>
+        <f>M92-M97-M102-M110</f>
         <v/>
       </c>
       <c r="N115" s="18">
-        <f>N80-(N85+N90)-N98</f>
+        <f>N92-N97-N102-N110</f>
         <v/>
       </c>
     </row>
@@ -6577,43 +6604,43 @@
         </is>
       </c>
       <c r="E116" s="22">
-        <f>IF(E92&gt;=$D$44,"PASS","LOCKED")</f>
+        <f>IF(E104&gt;=$D$55,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="F116" s="22">
-        <f>IF(F92&gt;=$D$44,"PASS","LOCKED")</f>
+        <f>IF(F104&gt;=$D$55,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="G116" s="22">
-        <f>IF(G92&gt;=$D$44,"PASS","LOCKED")</f>
+        <f>IF(G104&gt;=$D$55,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="H116" s="22">
-        <f>IF(H92&gt;=$D$44,"PASS","LOCKED")</f>
+        <f>IF(H104&gt;=$D$55,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="I116" s="22">
-        <f>IF(I92&gt;=$D$44,"PASS","LOCKED")</f>
+        <f>IF(I104&gt;=$D$55,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="J116" s="22">
-        <f>IF(J92&gt;=$D$44,"PASS","LOCKED")</f>
+        <f>IF(J104&gt;=$D$55,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="K116" s="22">
-        <f>IF(K92&gt;=$D$44,"PASS","LOCKED")</f>
+        <f>IF(K104&gt;=$D$55,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="L116" s="22">
-        <f>IF(L92&gt;=$D$44,"PASS","LOCKED")</f>
+        <f>IF(L104&gt;=$D$55,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="M116" s="22">
-        <f>IF(M92&gt;=$D$44,"PASS","LOCKED")</f>
+        <f>IF(M104&gt;=$D$55,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="N116" s="22">
-        <f>IF(N92&gt;=$D$44,"PASS","LOCKED")</f>
+        <f>IF(N104&gt;=$D$55,"PASS","LOCKED")</f>
         <v/>
       </c>
     </row>
@@ -6634,48 +6661,46 @@
         </is>
       </c>
       <c r="E117" s="7">
-        <f>IF(E104="PASS",MAX(0,E103),0)</f>
+        <f>IF(E116="PASS",MAX(0,E115),0)</f>
         <v/>
       </c>
       <c r="F117" s="7">
-        <f>IF(F104="PASS",MAX(0,F103),0)</f>
+        <f>IF(F116="PASS",MAX(0,F115),0)</f>
         <v/>
       </c>
       <c r="G117" s="7">
-        <f>IF(G104="PASS",MAX(0,G103),0)</f>
+        <f>IF(G116="PASS",MAX(0,G115),0)</f>
         <v/>
       </c>
       <c r="H117" s="7">
-        <f>IF(H104="PASS",MAX(0,H103),0)</f>
+        <f>IF(H116="PASS",MAX(0,H115),0)</f>
         <v/>
       </c>
       <c r="I117" s="7">
-        <f>IF(I104="PASS",MAX(0,I103),0)</f>
+        <f>IF(I116="PASS",MAX(0,I115),0)</f>
         <v/>
       </c>
       <c r="J117" s="7">
-        <f>IF(J104="PASS",MAX(0,J103),0)</f>
+        <f>IF(J116="PASS",MAX(0,J115),0)</f>
         <v/>
       </c>
       <c r="K117" s="7">
-        <f>IF(K104="PASS",MAX(0,K103),0)</f>
+        <f>IF(K116="PASS",MAX(0,K115),0)</f>
         <v/>
       </c>
       <c r="L117" s="7">
-        <f>IF(L104="PASS",MAX(0,L103),0)</f>
+        <f>IF(L116="PASS",MAX(0,L115),0)</f>
         <v/>
       </c>
       <c r="M117" s="7">
-        <f>IF(M104="PASS",MAX(0,M103),0)</f>
+        <f>IF(M116="PASS",MAX(0,M115),0)</f>
         <v/>
       </c>
       <c r="N117" s="7">
-        <f>IF(N104="PASS",MAX(0,N103),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="118"/>
-    <row r="119"/>
+        <f>IF(N116="PASS",MAX(0,N115),0)</f>
+        <v/>
+      </c>
+    </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
@@ -6718,7 +6743,7 @@
       </c>
       <c r="C122" s="6" t="inlineStr"/>
       <c r="D122" s="18">
-        <f>$D$17</f>
+        <f>$D$28</f>
         <v/>
       </c>
     </row>
@@ -6735,7 +6760,7 @@
       </c>
       <c r="C123" s="6" t="inlineStr"/>
       <c r="D123" s="18">
-        <f>$D$17*$D$18</f>
+        <f>$D$28*$D$29</f>
         <v/>
       </c>
     </row>
@@ -6752,7 +6777,7 @@
       </c>
       <c r="C124" s="6" t="inlineStr"/>
       <c r="D124" s="18">
-        <f>D96</f>
+        <f>E108</f>
         <v/>
       </c>
     </row>
@@ -6769,11 +6794,16 @@
       </c>
       <c r="C125" s="6" t="inlineStr"/>
       <c r="D125" s="7">
-        <f>D110+D111+D112</f>
-        <v/>
-      </c>
-    </row>
-    <row r="126"/>
+        <f>D122+D123+D124</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="D126">
+        <f>$D$28*$D$29</f>
+        <v/>
+      </c>
+    </row>
     <row r="127">
       <c r="A127" s="23" t="inlineStr">
         <is>
@@ -6782,6 +6812,10 @@
       </c>
       <c r="B127" s="6" t="inlineStr"/>
       <c r="C127" s="6" t="inlineStr"/>
+      <c r="D127">
+        <f>E108</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
@@ -6796,7 +6830,7 @@
       </c>
       <c r="C128" s="6" t="inlineStr"/>
       <c r="D128" s="18">
-        <f>$D$55</f>
+        <f>$D$28*$D$50</f>
         <v/>
       </c>
     </row>
@@ -6817,7 +6851,7 @@
         </is>
       </c>
       <c r="D129" s="18">
-        <f>D113-D116</f>
+        <f>D125-D128</f>
         <v/>
       </c>
     </row>
@@ -6834,7 +6868,7 @@
       </c>
       <c r="C130" s="6" t="inlineStr"/>
       <c r="D130" s="7">
-        <f>D116+D117</f>
+        <f>D128+D129</f>
         <v/>
       </c>
     </row>
@@ -6847,12 +6881,22 @@
       <c r="B131" s="6" t="inlineStr"/>
       <c r="C131" s="6" t="inlineStr"/>
       <c r="D131" s="10">
-        <f>IF(ABS(D113-D118)&lt;0.01,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="132"/>
-    <row r="133"/>
+        <f>$D$28*$D$50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="D132">
+        <f>D125-D130</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="D133">
+        <f>D131+D132</f>
+        <v/>
+      </c>
+    </row>
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
@@ -6889,6 +6933,10 @@
           <t>Exit Multiple × Exit Yr EBITDA</t>
         </is>
       </c>
+      <c r="D135">
+        <f>D128-D133</f>
+        <v/>
+      </c>
       <c r="K135" s="18">
         <f>$D$19*K74</f>
         <v/>
@@ -6957,7 +7005,12 @@
         <v/>
       </c>
     </row>
-    <row r="139"/>
+    <row r="139">
+      <c r="D139">
+        <f>K86</f>
+        <v/>
+      </c>
+    </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
@@ -6966,7 +7019,10 @@
       </c>
       <c r="B140" s="4" t="n"/>
       <c r="C140" s="4" t="n"/>
-      <c r="D140" s="4" t="n"/>
+      <c r="D140" s="4">
+        <f>D139*$D$30</f>
+        <v/>
+      </c>
       <c r="E140" s="4" t="n"/>
       <c r="F140" s="4" t="n"/>
       <c r="G140" s="4" t="n"/>
@@ -6991,7 +7047,7 @@
       </c>
       <c r="C141" s="6" t="inlineStr"/>
       <c r="D141" s="18">
-        <f>-D117</f>
+        <f>K103</f>
         <v/>
       </c>
       <c r="E141" s="18">
@@ -7052,7 +7108,7 @@
         </is>
       </c>
       <c r="D142" s="25">
-        <f>IRR(D129:K129)</f>
+        <f>K111</f>
         <v/>
       </c>
     </row>
@@ -7073,11 +7129,10 @@
         </is>
       </c>
       <c r="D143" s="24">
-        <f>SUMIF(D129:K129,"&gt;0")/ABS(D129)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="144"/>
+        <f>D140-D141+D142</f>
+        <v/>
+      </c>
+    </row>
     <row r="145">
       <c r="A145" s="23" t="inlineStr">
         <is>
@@ -7100,48 +7155,45 @@
       </c>
       <c r="C146" s="6" t="inlineStr"/>
       <c r="D146" s="18">
-        <f>-$D$17-D111</f>
+        <f>-D129</f>
         <v/>
       </c>
       <c r="E146" s="18">
-        <f>E80</f>
+        <f>E117</f>
         <v/>
       </c>
       <c r="F146" s="18">
-        <f>F80</f>
+        <f>F117</f>
         <v/>
       </c>
       <c r="G146" s="18">
-        <f>G80</f>
+        <f>G117</f>
         <v/>
       </c>
       <c r="H146" s="18">
-        <f>H80</f>
+        <f>H117</f>
         <v/>
       </c>
       <c r="I146" s="18">
-        <f>I80</f>
+        <f>I117</f>
         <v/>
       </c>
       <c r="J146" s="18">
-        <f>J80</f>
+        <f>J117</f>
         <v/>
       </c>
       <c r="K146" s="18">
-        <f>K80+K123</f>
-        <v/>
-      </c>
-      <c r="L146" s="18">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M146" s="18">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N146" s="18">
-        <f>0</f>
-        <v/>
+        <f>K117+D143</f>
+        <v/>
+      </c>
+      <c r="L146" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N146" s="18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -7161,7 +7213,13 @@
         </is>
       </c>
       <c r="D147" s="25">
-        <f>IRR(D134:K134)</f>
+        <f>IRR(D146:N146)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="D148" s="55">
+        <f>(SUM(E146:K146))/-D146</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Model_1_CCGT.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_1_CCGT.xlsx
@@ -3600,7 +3600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N148"/>
+  <dimension ref="A1:N149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -7006,6 +7006,11 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Exit EBITDA</t>
+        </is>
+      </c>
       <c r="D139">
         <f>K86</f>
         <v/>
@@ -7014,7 +7019,7 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>EQUITY RETURNS</t>
+          <t>Exit EV</t>
         </is>
       </c>
       <c r="B140" s="4" t="n"/>
@@ -7047,48 +7052,45 @@
       </c>
       <c r="C141" s="6" t="inlineStr"/>
       <c r="D141" s="18">
-        <f>K103</f>
+        <f>-D129</f>
         <v/>
       </c>
       <c r="E141" s="18">
-        <f>E105</f>
+        <f>E117</f>
         <v/>
       </c>
       <c r="F141" s="18">
-        <f>F105</f>
+        <f>F117</f>
         <v/>
       </c>
       <c r="G141" s="18">
-        <f>G105</f>
+        <f>G117</f>
         <v/>
       </c>
       <c r="H141" s="18">
-        <f>H105</f>
+        <f>H117</f>
         <v/>
       </c>
       <c r="I141" s="18">
-        <f>I105</f>
+        <f>I117</f>
         <v/>
       </c>
       <c r="J141" s="18">
-        <f>J105</f>
+        <f>J117</f>
         <v/>
       </c>
       <c r="K141" s="18">
-        <f>K105+K126</f>
-        <v/>
-      </c>
-      <c r="L141" s="18">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M141" s="18">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N141" s="18">
-        <f>0</f>
-        <v/>
+        <f>K117+D143</f>
+        <v/>
+      </c>
+      <c r="L141" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" s="18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -7108,14 +7110,14 @@
         </is>
       </c>
       <c r="D142" s="25">
-        <f>K111</f>
+        <f>IRR(D141:N141)</f>
         <v/>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>MOIC</t>
+          <t>Exit Equity Proceeds</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
@@ -7129,18 +7131,33 @@
         </is>
       </c>
       <c r="D143" s="24">
-        <f>D140-D141+D142</f>
+        <f>D140-D144+D145</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Exit Debt Balance</t>
+        </is>
+      </c>
+      <c r="D144">
+        <f>K103</f>
         <v/>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="23" t="inlineStr">
         <is>
-          <t>Unlevered Returns (for reference)</t>
+          <t>Exit DSRA Release</t>
         </is>
       </c>
       <c r="B145" s="6" t="inlineStr"/>
       <c r="C145" s="6" t="inlineStr"/>
+      <c r="D145">
+        <f>K111</f>
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
@@ -7199,7 +7216,7 @@
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>Unlevered IRR</t>
+          <t>MOIC</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
@@ -7212,8 +7229,8 @@
           <t>IRR of Equity CFs</t>
         </is>
       </c>
-      <c r="D147" s="25">
-        <f>IRR(D146:N146)</f>
+      <c r="D147" s="24">
+        <f>(SUM(E141:K141))/-D141</f>
         <v/>
       </c>
     </row>
@@ -7223,6 +7240,7 @@
         <v/>
       </c>
     </row>
+    <row r="149"/>
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="D7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/deliverables/deliverables-20260120-0030/Model_1_CCGT.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_1_CCGT.xlsx
@@ -3600,7 +3600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N149"/>
+  <dimension ref="A1:N148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3987,10 +3987,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr"/>
       <c r="C22" s="6" t="inlineStr"/>
-      <c r="D22" s="10">
-        <f>D132</f>
-        <v/>
-      </c>
+      <c r="D22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -7240,7 +7237,6 @@
         <v/>
       </c>
     </row>
-    <row r="149"/>
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="D7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/deliverables/deliverables-20260120-0030/Model_1_CCGT.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_1_CCGT.xlsx
@@ -3769,10 +3769,25 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="45" t="n"/>
-      <c r="B6" s="45" t="n"/>
-      <c r="C6" s="45" t="n"/>
-      <c r="D6" s="45" t="n"/>
+      <c r="A6" s="45" t="inlineStr">
+        <is>
+          <t>Min DSCR</t>
+        </is>
+      </c>
+      <c r="B6" s="45" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C6" s="45" t="inlineStr">
+        <is>
+          <t>Minimum debt service coverage ratio</t>
+        </is>
+      </c>
+      <c r="D6" s="55">
+        <f>IF(COUNTIF(E104:K104,"&gt;0")&gt;0,MINIFS(E104:K104,E104:K104,"&gt;0"),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="46" t="inlineStr">
@@ -4015,7 +4030,7 @@
         </is>
       </c>
       <c r="D24" s="10">
-        <f>IF(MIN(E104:K104)&gt;=1.25,"PASS","FAIL")</f>
+        <f>IF(D6&gt;=1.25,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
